--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.6770604099031926</v>
+        <v>0.6770604099031927</v>
       </c>
       <c r="C2">
         <v>0.5789242513682565</v>
       </c>
       <c r="D2">
-        <v>0.5649496127737718</v>
+        <v>0.5649496127737716</v>
       </c>
       <c r="E2">
-        <v>0.5804057579587106</v>
+        <v>0.5804057579587105</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -419,13 +419,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.5932758831987774</v>
+        <v>0.5932758831987773</v>
       </c>
       <c r="C4">
-        <v>0.4947602260979274</v>
+        <v>0.4947602260979275</v>
       </c>
       <c r="D4">
-        <v>0.4930538134380273</v>
+        <v>0.4930538134380272</v>
       </c>
       <c r="E4">
         <v>0.513683334417758</v>
@@ -436,13 +436,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.5932758831987774</v>
+        <v>0.5932758831987773</v>
       </c>
       <c r="C5">
-        <v>0.4947602260979274</v>
+        <v>0.4947602260979275</v>
       </c>
       <c r="D5">
-        <v>0.4930538134380274</v>
+        <v>0.4930538134380273</v>
       </c>
       <c r="E5">
         <v>0.513683334417758</v>
@@ -453,13 +453,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.5932758831987774</v>
+        <v>0.5932758831987773</v>
       </c>
       <c r="C6">
-        <v>0.4947602260979274</v>
+        <v>0.4947602260979275</v>
       </c>
       <c r="D6">
-        <v>0.4930538134380274</v>
+        <v>0.4930538134380273</v>
       </c>
       <c r="E6">
         <v>0.513683334417758</v>
@@ -470,13 +470,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.69720711251173</v>
+        <v>0.6972071125117298</v>
       </c>
       <c r="C7">
         <v>0.609372313844689</v>
       </c>
       <c r="D7">
-        <v>0.6219640689495456</v>
+        <v>0.6219640689495455</v>
       </c>
       <c r="E7">
         <v>0.6529644296755394</v>
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.69720711251173</v>
+        <v>0.6972071125117298</v>
       </c>
       <c r="C8">
         <v>0.6093723138446889</v>
@@ -496,7 +496,7 @@
         <v>0.6219640689495456</v>
       </c>
       <c r="E8">
-        <v>0.6529644296755395</v>
+        <v>0.6529644296755394</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -521,13 +521,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.6972071125117301</v>
+        <v>0.69720711251173</v>
       </c>
       <c r="C10">
-        <v>0.6093723138446889</v>
+        <v>0.609372313844689</v>
       </c>
       <c r="D10">
-        <v>0.6219640689495456</v>
+        <v>0.6219640689495455</v>
       </c>
       <c r="E10">
         <v>0.6529644296755394</v>
@@ -538,7 +538,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.6972071125117301</v>
+        <v>0.6972071125117298</v>
       </c>
       <c r="C11">
         <v>0.6093723138446889</v>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.6061705156093438</v>
+        <v>0.6061705156093437</v>
       </c>
       <c r="C12">
         <v>0.5183018079406878</v>
@@ -626,10 +626,10 @@
         <v>0.7063684421094018</v>
       </c>
       <c r="C16">
-        <v>0.6110309277526876</v>
+        <v>0.6110309277526877</v>
       </c>
       <c r="D16">
-        <v>0.6034273598420548</v>
+        <v>0.6034273598420546</v>
       </c>
       <c r="E16">
         <v>0.6108447296320033</v>
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.6061705156093438</v>
+        <v>0.6061705156093437</v>
       </c>
       <c r="C17">
         <v>0.5183018079406877</v>
       </c>
       <c r="D17">
-        <v>0.5139878124880423</v>
+        <v>0.5139878124880422</v>
       </c>
       <c r="E17">
         <v>0.5387437898893688</v>
@@ -663,7 +663,7 @@
         <v>0.57660336696369</v>
       </c>
       <c r="D18">
-        <v>0.5823614333274184</v>
+        <v>0.5823614333274183</v>
       </c>
       <c r="E18">
         <v>0.6207365870683349</v>
@@ -680,7 +680,7 @@
         <v>0.6110309277526876</v>
       </c>
       <c r="D19">
-        <v>0.6034273598420548</v>
+        <v>0.6034273598420546</v>
       </c>
       <c r="E19">
         <v>0.6108447296320033</v>
@@ -691,7 +691,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.7063684421094018</v>
+        <v>0.7063684421094019</v>
       </c>
       <c r="C20">
         <v>0.6110309277526876</v>
@@ -714,7 +714,7 @@
         <v>0.6110309277526876</v>
       </c>
       <c r="D21">
-        <v>0.6034273598420549</v>
+        <v>0.6034273598420548</v>
       </c>
       <c r="E21">
         <v>0.6108447296320033</v>
@@ -725,10 +725,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.7067773844880969</v>
+        <v>0.7067773844880967</v>
       </c>
       <c r="C22">
-        <v>0.5862965481334331</v>
+        <v>0.5862965481334332</v>
       </c>
       <c r="D22">
         <v>0.534325771103084</v>
@@ -742,7 +742,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.6770604099031926</v>
+        <v>0.6770604099031927</v>
       </c>
       <c r="C23">
         <v>0.5789242513682565</v>
@@ -751,7 +751,7 @@
         <v>0.5649496127737718</v>
       </c>
       <c r="E23">
-        <v>0.5804057579587106</v>
+        <v>0.5804057579587105</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -759,7 +759,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.516375247254754</v>
+        <v>0.5163752472547539</v>
       </c>
       <c r="C24">
         <v>0.4223558550269567</v>
@@ -768,7 +768,7 @@
         <v>0.4009189412880479</v>
       </c>
       <c r="E24">
-        <v>0.4074054610414095</v>
+        <v>0.4074054610414096</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -785,7 +785,7 @@
         <v>0.4009189412880478</v>
       </c>
       <c r="E25">
-        <v>0.4074054610414095</v>
+        <v>0.4074054610414096</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -793,7 +793,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.516375247254754</v>
+        <v>0.5163752472547539</v>
       </c>
       <c r="C26">
         <v>0.4223558550269567</v>
@@ -819,7 +819,7 @@
         <v>0.5597541856551072</v>
       </c>
       <c r="E27">
-        <v>0.5590570792150914</v>
+        <v>0.5590570792150915</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -836,7 +836,7 @@
         <v>0.5597541856551073</v>
       </c>
       <c r="E28">
-        <v>0.5590570792150914</v>
+        <v>0.5590570792150915</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -850,7 +850,7 @@
         <v>0.5860618912073483</v>
       </c>
       <c r="D29">
-        <v>0.5597541856551073</v>
+        <v>0.5597541856551072</v>
       </c>
       <c r="E29">
         <v>0.5590570792150915</v>
@@ -901,10 +901,10 @@
         <v>0.7947464499851491</v>
       </c>
       <c r="D32">
-        <v>0.842768349271545</v>
+        <v>0.8427683492715451</v>
       </c>
       <c r="E32">
-        <v>0.7983191071929628</v>
+        <v>0.798319107192963</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -918,7 +918,7 @@
         <v>0.8363987219585732</v>
       </c>
       <c r="D33">
-        <v>0.8902716640511406</v>
+        <v>0.8902716640511408</v>
       </c>
       <c r="E33">
         <v>0.8416216226974813</v>
@@ -932,13 +932,13 @@
         <v>0.843182037104559</v>
       </c>
       <c r="C34">
-        <v>0.819979080702392</v>
+        <v>0.8199790807023923</v>
       </c>
       <c r="D34">
-        <v>0.8431860182922102</v>
+        <v>0.8431860182922104</v>
       </c>
       <c r="E34">
-        <v>0.780416211257499</v>
+        <v>0.7804162112574989</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -946,16 +946,16 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.8870458969766211</v>
+        <v>0.887045896976621</v>
       </c>
       <c r="C35">
         <v>0.877500240323756</v>
       </c>
       <c r="D35">
-        <v>0.8796147183507463</v>
+        <v>0.8796147183507464</v>
       </c>
       <c r="E35">
-        <v>0.8110338517766937</v>
+        <v>0.8110338517766938</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -963,16 +963,16 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.7178968527387888</v>
+        <v>0.7178968527387889</v>
       </c>
       <c r="C36">
-        <v>0.7230162642562417</v>
+        <v>0.7230162642562418</v>
       </c>
       <c r="D36">
-        <v>0.7880090135660325</v>
+        <v>0.7880090135660327</v>
       </c>
       <c r="E36">
-        <v>0.7559735177276655</v>
+        <v>0.7559735177276654</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -980,10 +980,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.8443187564018223</v>
+        <v>0.8443187564018224</v>
       </c>
       <c r="C37">
-        <v>0.8716251719536564</v>
+        <v>0.8716251719536565</v>
       </c>
       <c r="D37">
         <v>0.918258919025586</v>
@@ -1017,13 +1017,13 @@
         <v>0.8900622408431595</v>
       </c>
       <c r="C39">
-        <v>0.895866275012857</v>
+        <v>0.8958662750128571</v>
       </c>
       <c r="D39">
         <v>0.9284640193509149</v>
       </c>
       <c r="E39">
-        <v>0.8566802789714666</v>
+        <v>0.8566802789714664</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1037,7 +1037,7 @@
         <v>0.8493397960129581</v>
       </c>
       <c r="D40">
-        <v>0.8537816226893136</v>
+        <v>0.8537816226893137</v>
       </c>
       <c r="E40">
         <v>0.7788077771816078</v>
@@ -1048,16 +1048,16 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.8870458969766211</v>
+        <v>0.887045896976621</v>
       </c>
       <c r="C41">
-        <v>0.877500240323756</v>
+        <v>0.8775002403237561</v>
       </c>
       <c r="D41">
-        <v>0.8796147183507463</v>
+        <v>0.8796147183507466</v>
       </c>
       <c r="E41">
-        <v>0.8110338517766937</v>
+        <v>0.8110338517766938</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1068,7 +1068,7 @@
         <v>0.7845052409119215</v>
       </c>
       <c r="C42">
-        <v>0.7852213501739191</v>
+        <v>0.7852213501739194</v>
       </c>
       <c r="D42">
         <v>0.8245622635555749</v>
@@ -1085,7 +1085,7 @@
         <v>0.757194188111128</v>
       </c>
       <c r="C43">
-        <v>0.7436581384572718</v>
+        <v>0.743658138457272</v>
       </c>
       <c r="D43">
         <v>0.7691437280376289</v>
@@ -1108,7 +1108,7 @@
         <v>0.6110829817922375</v>
       </c>
       <c r="E44">
-        <v>0.5863422560010912</v>
+        <v>0.586342256001091</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1116,7 +1116,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0.7256055114657837</v>
+        <v>0.7256055114657838</v>
       </c>
       <c r="C45">
         <v>0.7230294423355492</v>
@@ -1136,10 +1136,10 @@
         <v>0.8284892555294363</v>
       </c>
       <c r="C46">
-        <v>0.8316464855411975</v>
+        <v>0.8316464855411976</v>
       </c>
       <c r="D46">
-        <v>0.8713521470037082</v>
+        <v>0.8713521470037083</v>
       </c>
       <c r="E46">
         <v>0.8112325381004899</v>
@@ -1150,16 +1150,16 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>0.6613619286415678</v>
+        <v>0.661361928641568</v>
       </c>
       <c r="C47">
-        <v>0.6353215656400638</v>
+        <v>0.6353215656400639</v>
       </c>
       <c r="D47">
-        <v>0.6890606416922612</v>
+        <v>0.6890606416922611</v>
       </c>
       <c r="E47">
-        <v>0.6667130618788636</v>
+        <v>0.6667130618788634</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1173,7 +1173,7 @@
         <v>0.6844180593292025</v>
       </c>
       <c r="D48">
-        <v>0.7163432749471819</v>
+        <v>0.7163432749471818</v>
       </c>
       <c r="E48">
         <v>0.6858511042043088</v>
@@ -1184,13 +1184,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>0.6799097749129461</v>
+        <v>0.6799097749129462</v>
       </c>
       <c r="C49">
         <v>0.6102266192668748</v>
       </c>
       <c r="D49">
-        <v>0.6600343636540494</v>
+        <v>0.6600343636540493</v>
       </c>
       <c r="E49">
         <v>0.7244115876091015</v>
@@ -1218,7 +1218,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>0.5434823831423141</v>
+        <v>0.5434823831423142</v>
       </c>
       <c r="C51">
         <v>0.4807777867605427</v>
@@ -1238,13 +1238,13 @@
         <v>0.515142873936873</v>
       </c>
       <c r="C52">
-        <v>0.4528174007754976</v>
+        <v>0.4528174007754975</v>
       </c>
       <c r="D52">
-        <v>0.4835328654175808</v>
+        <v>0.4835328654175807</v>
       </c>
       <c r="E52">
-        <v>0.5462140007552516</v>
+        <v>0.5462140007552514</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1261,7 +1261,7 @@
         <v>0.6069358635910928</v>
       </c>
       <c r="E53">
-        <v>0.6736764002491603</v>
+        <v>0.6736764002491605</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1306,7 +1306,7 @@
         <v>0.7224486730287843</v>
       </c>
       <c r="C56">
-        <v>0.6366313752664382</v>
+        <v>0.6366313752664384</v>
       </c>
       <c r="D56">
         <v>0.6522465644373291</v>
@@ -1320,7 +1320,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>0.5535178990298961</v>
+        <v>0.553517899029896</v>
       </c>
       <c r="C57">
         <v>0.4724524488631562</v>
@@ -1329,7 +1329,7 @@
         <v>0.4926114920049406</v>
       </c>
       <c r="E57">
-        <v>0.5410690067859686</v>
+        <v>0.5410690067859687</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1340,13 +1340,13 @@
         <v>0.7695238305907963</v>
       </c>
       <c r="C58">
-        <v>0.6588922736763193</v>
+        <v>0.6588922736763194</v>
       </c>
       <c r="D58">
-        <v>0.6434247660695344</v>
+        <v>0.6434247660695342</v>
       </c>
       <c r="E58">
-        <v>0.6567430507440697</v>
+        <v>0.6567430507440698</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1354,7 +1354,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>0.7695238305907963</v>
+        <v>0.7695238305907964</v>
       </c>
       <c r="C59">
         <v>0.6588922736763194</v>
@@ -1363,7 +1363,7 @@
         <v>0.6434247660695342</v>
       </c>
       <c r="E59">
-        <v>0.6567430507440697</v>
+        <v>0.6567430507440698</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1380,7 +1380,7 @@
         <v>0.4564173141613587</v>
       </c>
       <c r="E60">
-        <v>0.4654238246015606</v>
+        <v>0.4654238246015607</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1388,16 +1388,16 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.568808340821932</v>
+        <v>0.5688083408219321</v>
       </c>
       <c r="C61">
         <v>0.4801988156712858</v>
       </c>
       <c r="D61">
-        <v>0.4564173141613588</v>
+        <v>0.4564173141613587</v>
       </c>
       <c r="E61">
-        <v>0.4654238246015606</v>
+        <v>0.4654238246015607</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1405,7 +1405,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>0.3346300284418046</v>
+        <v>0.3346300284418045</v>
       </c>
       <c r="C62">
         <v>0.2708702243127799</v>
@@ -1414,7 +1414,7 @@
         <v>0.2562736837921841</v>
       </c>
       <c r="E62">
-        <v>0.2708024213887155</v>
+        <v>0.2708024213887156</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1422,7 +1422,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>0.3346300284418046</v>
+        <v>0.3346300284418045</v>
       </c>
       <c r="C63">
         <v>0.2708702243127799</v>
@@ -1431,7 +1431,7 @@
         <v>0.2562736837921841</v>
       </c>
       <c r="E63">
-        <v>0.2708024213887155</v>
+        <v>0.2708024213887156</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1439,7 +1439,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>0.2305350604571148</v>
+        <v>0.2305350604571147</v>
       </c>
       <c r="C64">
         <v>0.185696632025683</v>
@@ -1473,16 +1473,16 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>0.9064815164799664</v>
+        <v>0.9064815164799666</v>
       </c>
       <c r="C66">
-        <v>0.8318222252052231</v>
+        <v>0.8318222252052232</v>
       </c>
       <c r="D66">
         <v>0.7883161282582776</v>
       </c>
       <c r="E66">
-        <v>0.7057978958032961</v>
+        <v>0.705797895803296</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,7 +1493,7 @@
         <v>0.8717658648493042</v>
       </c>
       <c r="C67">
-        <v>0.7835312456637349</v>
+        <v>0.7835312456637351</v>
       </c>
       <c r="D67">
         <v>0.7313519169557465</v>
@@ -1510,7 +1510,7 @@
         <v>0.9064815164799666</v>
       </c>
       <c r="C68">
-        <v>0.8318222252052231</v>
+        <v>0.8318222252052232</v>
       </c>
       <c r="D68">
         <v>0.7883161282582776</v>
@@ -1524,16 +1524,16 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>0.8717658648493041</v>
+        <v>0.8717658648493043</v>
       </c>
       <c r="C69">
-        <v>0.7835312456637349</v>
+        <v>0.783531245663735</v>
       </c>
       <c r="D69">
         <v>0.7313519169557465</v>
       </c>
       <c r="E69">
-        <v>0.6635115959465699</v>
+        <v>0.6635115959465698</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1544,7 +1544,7 @@
         <v>0.8717658648493041</v>
       </c>
       <c r="C70">
-        <v>0.7835312456637349</v>
+        <v>0.783531245663735</v>
       </c>
       <c r="D70">
         <v>0.7313519169557465</v>
@@ -1561,7 +1561,7 @@
         <v>0.8671033936050396</v>
       </c>
       <c r="C71">
-        <v>0.7635149225175585</v>
+        <v>0.7635149225175584</v>
       </c>
       <c r="D71">
         <v>0.7304157057048625</v>
@@ -1575,13 +1575,13 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>0.8403967231673921</v>
+        <v>0.8403967231673922</v>
       </c>
       <c r="C72">
-        <v>0.7363180970142041</v>
+        <v>0.7363180970142044</v>
       </c>
       <c r="D72">
-        <v>0.6919593503726609</v>
+        <v>0.6919593503726611</v>
       </c>
       <c r="E72">
         <v>0.6237308117000442</v>
@@ -1595,13 +1595,13 @@
         <v>0.8403967231673921</v>
       </c>
       <c r="C73">
-        <v>0.7363180970142041</v>
+        <v>0.7363180970142044</v>
       </c>
       <c r="D73">
-        <v>0.6919593503726609</v>
+        <v>0.6919593503726611</v>
       </c>
       <c r="E73">
-        <v>0.6237308117000442</v>
+        <v>0.623730811700044</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1609,16 +1609,16 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>0.8403967231673921</v>
+        <v>0.8403967231673922</v>
       </c>
       <c r="C74">
-        <v>0.7363180970142041</v>
+        <v>0.7363180970142044</v>
       </c>
       <c r="D74">
-        <v>0.6919593503726609</v>
+        <v>0.6919593503726611</v>
       </c>
       <c r="E74">
-        <v>0.6237308117000442</v>
+        <v>0.623730811700044</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1635,7 +1635,7 @@
         <v>0.5736212235261697</v>
       </c>
       <c r="E75">
-        <v>0.5080040544266964</v>
+        <v>0.5080040544266965</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1643,10 +1643,10 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>0.8717658648493039</v>
+        <v>0.8717658648493041</v>
       </c>
       <c r="C76">
-        <v>0.7835312456637349</v>
+        <v>0.7835312456637351</v>
       </c>
       <c r="D76">
         <v>0.7313519169557465</v>
@@ -1666,7 +1666,7 @@
         <v>0.7669710875462793</v>
       </c>
       <c r="D77">
-        <v>0.6892411990989552</v>
+        <v>0.6892411990989553</v>
       </c>
       <c r="E77">
         <v>0.6059719782358408</v>
@@ -1686,7 +1686,7 @@
         <v>0.6892411990989552</v>
       </c>
       <c r="E78">
-        <v>0.6059719782358407</v>
+        <v>0.6059719782358408</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1703,7 +1703,7 @@
         <v>0.6892411990989553</v>
       </c>
       <c r="E79">
-        <v>0.6059719782358407</v>
+        <v>0.6059719782358408</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1728,13 +1728,13 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>0.8744042778993142</v>
+        <v>0.8744042778993143</v>
       </c>
       <c r="C81">
         <v>0.7911856302734517</v>
       </c>
       <c r="D81">
-        <v>0.7851184453387094</v>
+        <v>0.7851184453387097</v>
       </c>
       <c r="E81">
         <v>0.7349622985367303</v>
@@ -1751,7 +1751,7 @@
         <v>0.7911856302734517</v>
       </c>
       <c r="D82">
-        <v>0.7851184453387096</v>
+        <v>0.7851184453387097</v>
       </c>
       <c r="E82">
         <v>0.7349622985367303</v>
@@ -1799,13 +1799,13 @@
         <v>0.7467224045565621</v>
       </c>
       <c r="C85">
-        <v>0.6727821780652352</v>
+        <v>0.6727821780652354</v>
       </c>
       <c r="D85">
         <v>0.616141316355184</v>
       </c>
       <c r="E85">
-        <v>0.5400683437025028</v>
+        <v>0.5400683437025027</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1816,10 +1816,10 @@
         <v>0.7467224045565621</v>
       </c>
       <c r="C86">
-        <v>0.6727821780652352</v>
+        <v>0.6727821780652354</v>
       </c>
       <c r="D86">
-        <v>0.6161413163551839</v>
+        <v>0.616141316355184</v>
       </c>
       <c r="E86">
         <v>0.5400683437025028</v>
@@ -1830,7 +1830,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>0.8138698100562691</v>
+        <v>0.813869810056269</v>
       </c>
       <c r="C87">
         <v>0.7166610758508382</v>
@@ -1839,7 +1839,7 @@
         <v>0.6334906786091909</v>
       </c>
       <c r="E87">
-        <v>0.5545195134349676</v>
+        <v>0.5545195134349675</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1856,7 +1856,7 @@
         <v>0.6334906786091908</v>
       </c>
       <c r="E88">
-        <v>0.5545195134349676</v>
+        <v>0.5545195134349675</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1873,7 +1873,7 @@
         <v>0.6334906786091908</v>
       </c>
       <c r="E89">
-        <v>0.5545195134349676</v>
+        <v>0.5545195134349675</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1921,7 +1921,7 @@
         <v>1.523621984017227</v>
       </c>
       <c r="D92">
-        <v>1.714013274111475</v>
+        <v>1.714013274111476</v>
       </c>
       <c r="E92">
         <v>1.591292987913244</v>
@@ -2108,7 +2108,7 @@
         <v>1.239060393570554</v>
       </c>
       <c r="D103">
-        <v>1.352607615695029</v>
+        <v>1.35260761569503</v>
       </c>
       <c r="E103">
         <v>1.275995510636288</v>
@@ -2190,7 +2190,7 @@
         <v>1.070690560576943</v>
       </c>
       <c r="C108">
-        <v>1.108674640198209</v>
+        <v>1.10867464019821</v>
       </c>
       <c r="D108">
         <v>1.208487033193066</v>
@@ -2210,7 +2210,7 @@
         <v>1.102864338696351</v>
       </c>
       <c r="D109">
-        <v>1.207783413951536</v>
+        <v>1.207783413951537</v>
       </c>
       <c r="E109">
         <v>1.182405834085744</v>
@@ -2357,7 +2357,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>0.9075442550245343</v>
+        <v>0.9075442550245342</v>
       </c>
       <c r="C118">
         <v>0.9133576216203363</v>
@@ -2380,10 +2380,10 @@
         <v>0.9156355341890277</v>
       </c>
       <c r="D119">
-        <v>0.9856019482451996</v>
+        <v>0.9856019482451998</v>
       </c>
       <c r="E119">
-        <v>0.9844348154283181</v>
+        <v>0.9844348154283182</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2400,7 +2400,7 @@
         <v>1.549468623682753</v>
       </c>
       <c r="E120">
-        <v>1.485051719824985</v>
+        <v>1.485051719824986</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2417,7 +2417,7 @@
         <v>1.549468623682753</v>
       </c>
       <c r="E121">
-        <v>1.485051719824985</v>
+        <v>1.485051719824986</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2493,10 +2493,10 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>1.023327342765816</v>
+        <v>1.023327342765817</v>
       </c>
       <c r="C126">
-        <v>1.050177481678078</v>
+        <v>1.050177481678079</v>
       </c>
       <c r="D126">
         <v>1.139874734923805</v>
@@ -2513,7 +2513,7 @@
         <v>1.076175490377606</v>
       </c>
       <c r="C127">
-        <v>1.105096264000139</v>
+        <v>1.10509626400014</v>
       </c>
       <c r="D127">
         <v>1.191469465369372</v>
@@ -2578,7 +2578,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>1.354729459210792</v>
+        <v>1.354729459210793</v>
       </c>
       <c r="C131">
         <v>1.453378033190769</v>
@@ -2652,7 +2652,7 @@
         <v>1.386086806336798</v>
       </c>
       <c r="D135">
-        <v>1.494231151041391</v>
+        <v>1.494231151041392</v>
       </c>
       <c r="E135">
         <v>1.39455111704644</v>
@@ -2669,7 +2669,7 @@
         <v>1.298520697239982</v>
       </c>
       <c r="D136">
-        <v>1.37932538555345</v>
+        <v>1.379325385553451</v>
       </c>
       <c r="E136">
         <v>1.26931932249185</v>
@@ -2686,7 +2686,7 @@
         <v>1.296394165120965</v>
       </c>
       <c r="D137">
-        <v>1.375187571032221</v>
+        <v>1.375187571032222</v>
       </c>
       <c r="E137">
         <v>1.269691266490287</v>
@@ -2703,7 +2703,7 @@
         <v>1.296394165120965</v>
       </c>
       <c r="D138">
-        <v>1.375187571032221</v>
+        <v>1.375187571032222</v>
       </c>
       <c r="E138">
         <v>1.269691266490287</v>
@@ -3006,7 +3006,7 @@
         <v>1.025107230490702</v>
       </c>
       <c r="C156">
-        <v>1.065431110713732</v>
+        <v>1.065431110713733</v>
       </c>
       <c r="D156">
         <v>1.093407148652094</v>
@@ -3023,7 +3023,7 @@
         <v>1.019028362702638</v>
       </c>
       <c r="C157">
-        <v>1.038785996784933</v>
+        <v>1.038785996784934</v>
       </c>
       <c r="D157">
         <v>1.063283014061067</v>
@@ -3063,7 +3063,7 @@
         <v>1.236338962498405</v>
       </c>
       <c r="E159">
-        <v>1.143292353399533</v>
+        <v>1.143292353399532</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3080,7 +3080,7 @@
         <v>1.085453080546463</v>
       </c>
       <c r="E160">
-        <v>1.008541167734632</v>
+        <v>1.008541167734633</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3105,7 +3105,7 @@
         <v>161</v>
       </c>
       <c r="B162">
-        <v>0.959731719391267</v>
+        <v>0.9597317193912669</v>
       </c>
       <c r="C162">
         <v>0.9743994763152179</v>
@@ -3131,7 +3131,7 @@
         <v>1.268151400684942</v>
       </c>
       <c r="E163">
-        <v>1.187371665679263</v>
+        <v>1.187371665679262</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3193,13 +3193,13 @@
         <v>0.9473828388919421</v>
       </c>
       <c r="C167">
-        <v>0.9639299250047068</v>
+        <v>0.9639299250047069</v>
       </c>
       <c r="D167">
         <v>1.011544375508533</v>
       </c>
       <c r="E167">
-        <v>0.9558914590065104</v>
+        <v>0.9558914590065102</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3213,10 +3213,10 @@
         <v>0.8780855871632011</v>
       </c>
       <c r="D168">
-        <v>0.9213239353944722</v>
+        <v>0.9213239353944723</v>
       </c>
       <c r="E168">
-        <v>0.8780949549032323</v>
+        <v>0.8780949549032319</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3247,7 +3247,7 @@
         <v>1.412635865675608</v>
       </c>
       <c r="D170">
-        <v>1.539453288136813</v>
+        <v>1.539453288136814</v>
       </c>
       <c r="E170">
         <v>1.43596347252841</v>
@@ -3278,7 +3278,7 @@
         <v>1.318189102729343</v>
       </c>
       <c r="C172">
-        <v>1.405926067570613</v>
+        <v>1.405926067570614</v>
       </c>
       <c r="D172">
         <v>1.52876627957461</v>
@@ -3309,7 +3309,7 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>1.333111522851883</v>
+        <v>1.333111522851882</v>
       </c>
       <c r="C174">
         <v>1.423309826232593</v>
@@ -3343,7 +3343,7 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>1.182158336262909</v>
+        <v>1.18215833626291</v>
       </c>
       <c r="C176">
         <v>1.242657224362127</v>
@@ -3394,7 +3394,7 @@
         <v>178</v>
       </c>
       <c r="B179">
-        <v>1.168352510096963</v>
+        <v>1.168352510096964</v>
       </c>
       <c r="C179">
         <v>1.225506224267042</v>
@@ -3471,7 +3471,7 @@
         <v>1.0414028516265</v>
       </c>
       <c r="E183">
-        <v>0.9338249238349717</v>
+        <v>0.9338249238349716</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,7 +3482,7 @@
         <v>1.115186593811863</v>
       </c>
       <c r="C184">
-        <v>1.138721402193903</v>
+        <v>1.138721402193902</v>
       </c>
       <c r="D184">
         <v>1.15590740102506</v>
@@ -3499,7 +3499,7 @@
         <v>1.115186593811863</v>
       </c>
       <c r="C185">
-        <v>1.138721402193903</v>
+        <v>1.138721402193902</v>
       </c>
       <c r="D185">
         <v>1.15590740102506</v>
@@ -3516,7 +3516,7 @@
         <v>1.033720238338321</v>
       </c>
       <c r="C186">
-        <v>1.043027606644746</v>
+        <v>1.043027606644747</v>
       </c>
       <c r="D186">
         <v>1.052024907249437</v>
@@ -3547,7 +3547,7 @@
         <v>187</v>
       </c>
       <c r="B188">
-        <v>1.019453893865384</v>
+        <v>1.019453893865385</v>
       </c>
       <c r="C188">
         <v>1.025474320377279</v>
@@ -3564,7 +3564,7 @@
         <v>188</v>
       </c>
       <c r="B189">
-        <v>1.006323013379187</v>
+        <v>1.006323013379188</v>
       </c>
       <c r="C189">
         <v>0.9973127684143225</v>
@@ -3573,7 +3573,7 @@
         <v>1.003882645453216</v>
       </c>
       <c r="E189">
-        <v>0.9136794045303314</v>
+        <v>0.9136794045303313</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3581,7 +3581,7 @@
         <v>189</v>
       </c>
       <c r="B190">
-        <v>1.006323013379187</v>
+        <v>1.006323013379188</v>
       </c>
       <c r="C190">
         <v>0.9973127684143225</v>
@@ -3590,7 +3590,7 @@
         <v>1.003882645453216</v>
       </c>
       <c r="E190">
-        <v>0.9136794045303314</v>
+        <v>0.9136794045303313</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3655,7 +3655,7 @@
         <v>1.390204356009664</v>
       </c>
       <c r="D194">
-        <v>1.538098040434344</v>
+        <v>1.538098040434345</v>
       </c>
       <c r="E194">
         <v>1.435259613041828</v>
@@ -3689,10 +3689,10 @@
         <v>1.302460579853198</v>
       </c>
       <c r="D196">
-        <v>1.406938510853498</v>
+        <v>1.406938510853499</v>
       </c>
       <c r="E196">
-        <v>1.310470793836473</v>
+        <v>1.310470793836474</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3740,10 +3740,10 @@
         <v>1.229980107580802</v>
       </c>
       <c r="D199">
-        <v>1.323361826469083</v>
+        <v>1.323361826469084</v>
       </c>
       <c r="E199">
-        <v>1.251997918818898</v>
+        <v>1.251997918818897</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3771,10 +3771,10 @@
         <v>1.118460480396674</v>
       </c>
       <c r="C201">
-        <v>1.17636193646718</v>
+        <v>1.176361936467181</v>
       </c>
       <c r="D201">
-        <v>1.285653448477669</v>
+        <v>1.28565344847767</v>
       </c>
       <c r="E201">
         <v>1.236834222772002</v>
@@ -3819,7 +3819,7 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>1.112804053576242</v>
+        <v>1.112804053576243</v>
       </c>
       <c r="C204">
         <v>1.177159435651853</v>
@@ -3856,7 +3856,7 @@
         <v>1.017747997185505</v>
       </c>
       <c r="C206">
-        <v>0.9966806884495133</v>
+        <v>0.9966806884495135</v>
       </c>
       <c r="D206">
         <v>1.107100727163361</v>
@@ -3870,10 +3870,10 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>0.9622790333999796</v>
+        <v>0.9622790333999793</v>
       </c>
       <c r="C207">
-        <v>0.9254740055761235</v>
+        <v>0.9254740055761236</v>
       </c>
       <c r="D207">
         <v>1.007024554003531</v>
@@ -3890,13 +3890,13 @@
         <v>0.9622790333999796</v>
       </c>
       <c r="C208">
-        <v>0.9254740055761234</v>
+        <v>0.9254740055761236</v>
       </c>
       <c r="D208">
         <v>1.007024554003531</v>
       </c>
       <c r="E208">
-        <v>1.012381411855388</v>
+        <v>1.012381411855389</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3924,7 +3924,7 @@
         <v>0.9622790333999796</v>
       </c>
       <c r="C210">
-        <v>0.9254740055761235</v>
+        <v>0.9254740055761236</v>
       </c>
       <c r="D210">
         <v>1.007024554003532</v>
@@ -3944,7 +3944,7 @@
         <v>0.863549902956287</v>
       </c>
       <c r="D211">
-        <v>0.9387114888060535</v>
+        <v>0.9387114888060537</v>
       </c>
       <c r="E211">
         <v>0.9673493736767678</v>
@@ -3975,7 +3975,7 @@
         <v>0.9622790333999796</v>
       </c>
       <c r="C213">
-        <v>0.9254740055761232</v>
+        <v>0.9254740055761236</v>
       </c>
       <c r="D213">
         <v>1.007024554003532</v>
@@ -4006,10 +4006,10 @@
         <v>214</v>
       </c>
       <c r="B215">
-        <v>0.8887276455136686</v>
+        <v>0.8887276455136685</v>
       </c>
       <c r="C215">
-        <v>0.8309831786397842</v>
+        <v>0.8309831786397844</v>
       </c>
       <c r="D215">
         <v>0.8833553007108405</v>
@@ -4023,7 +4023,7 @@
         <v>215</v>
       </c>
       <c r="B216">
-        <v>0.828729256776093</v>
+        <v>0.8287292567760928</v>
       </c>
       <c r="C216">
         <v>0.7646241560306528</v>
@@ -4040,7 +4040,7 @@
         <v>216</v>
       </c>
       <c r="B217">
-        <v>0.8331956009854593</v>
+        <v>0.8331956009854592</v>
       </c>
       <c r="C217">
         <v>0.7818212031001772</v>
@@ -4049,7 +4049,7 @@
         <v>0.8358257333909137</v>
       </c>
       <c r="E217">
-        <v>0.8525912380620226</v>
+        <v>0.8525912380620224</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4066,7 +4066,7 @@
         <v>0.7930059510763433</v>
       </c>
       <c r="E218">
-        <v>0.8131915384599778</v>
+        <v>0.8131915384599777</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4074,16 +4074,16 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>0.8848933395314343</v>
+        <v>0.8848933395314345</v>
       </c>
       <c r="C219">
         <v>0.8500934280665252</v>
       </c>
       <c r="D219">
-        <v>0.926610429539609</v>
+        <v>0.9266104295396088</v>
       </c>
       <c r="E219">
-        <v>0.954393506956594</v>
+        <v>0.9543935069565939</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,7 +4091,7 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>0.8790936470525484</v>
+        <v>0.8790936470525483</v>
       </c>
       <c r="C220">
         <v>0.8397846735274516</v>
@@ -4100,7 +4100,7 @@
         <v>0.9175554479705944</v>
       </c>
       <c r="E220">
-        <v>0.9457878068827578</v>
+        <v>0.9457878068827575</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4108,7 +4108,7 @@
         <v>220</v>
       </c>
       <c r="B221">
-        <v>0.8689748227910361</v>
+        <v>0.8689748227910362</v>
       </c>
       <c r="C221">
         <v>0.8115127542183835</v>
@@ -4117,7 +4117,7 @@
         <v>0.8790897593788863</v>
       </c>
       <c r="E221">
-        <v>0.9039684963447373</v>
+        <v>0.9039684963447374</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4134,7 +4134,7 @@
         <v>0.926610429539609</v>
       </c>
       <c r="E222">
-        <v>0.954393506956594</v>
+        <v>0.9543935069565939</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4165,10 +4165,10 @@
         <v>0.7613236699133776</v>
       </c>
       <c r="D224">
-        <v>0.7784293209533373</v>
+        <v>0.7784293209533371</v>
       </c>
       <c r="E224">
-        <v>0.8083381728002521</v>
+        <v>0.808338172800252</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4182,7 +4182,7 @@
         <v>0.8297753604139291</v>
       </c>
       <c r="D225">
-        <v>0.8579198834500513</v>
+        <v>0.8579198834500512</v>
       </c>
       <c r="E225">
         <v>0.8734091216336787</v>
@@ -4193,13 +4193,13 @@
         <v>225</v>
       </c>
       <c r="B226">
-        <v>0.8821923919525474</v>
+        <v>0.8821923919525475</v>
       </c>
       <c r="C226">
-        <v>0.7976902111994986</v>
+        <v>0.7976902111994987</v>
       </c>
       <c r="D226">
-        <v>0.8229271729261516</v>
+        <v>0.8229271729261514</v>
       </c>
       <c r="E226">
         <v>0.8409629615485748</v>
@@ -4213,13 +4213,13 @@
         <v>0.9065768168383311</v>
       </c>
       <c r="C227">
-        <v>0.8506789758270924</v>
+        <v>0.8506789758270926</v>
       </c>
       <c r="D227">
         <v>0.8860338216824505</v>
       </c>
       <c r="E227">
-        <v>0.9007595330375899</v>
+        <v>0.90075953303759</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4244,7 +4244,7 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>0.8790936470525484</v>
+        <v>0.8790936470525483</v>
       </c>
       <c r="C229">
         <v>0.8397846735274515</v>
@@ -4253,7 +4253,7 @@
         <v>0.9175554479705945</v>
       </c>
       <c r="E229">
-        <v>0.9457878068827578</v>
+        <v>0.9457878068827575</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4284,10 +4284,10 @@
         <v>0.8183696453853562</v>
       </c>
       <c r="D231">
-        <v>0.9032906893370944</v>
+        <v>0.9032906893370943</v>
       </c>
       <c r="E231">
-        <v>0.9392849041849228</v>
+        <v>0.9392849041849229</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4295,13 +4295,13 @@
         <v>231</v>
       </c>
       <c r="B232">
-        <v>0.8357362071390887</v>
+        <v>0.8357362071390886</v>
       </c>
       <c r="C232">
         <v>0.7750757183582186</v>
       </c>
       <c r="D232">
-        <v>0.8465166628409109</v>
+        <v>0.8465166628409108</v>
       </c>
       <c r="E232">
         <v>0.8748958752347339</v>
@@ -4329,13 +4329,13 @@
         <v>233</v>
       </c>
       <c r="B234">
-        <v>0.8322742870251416</v>
+        <v>0.8322742870251414</v>
       </c>
       <c r="C234">
         <v>0.7758966757825618</v>
       </c>
       <c r="D234">
-        <v>0.8568097147472645</v>
+        <v>0.8568097147472644</v>
       </c>
       <c r="E234">
         <v>0.9014744274813183</v>
@@ -4346,13 +4346,13 @@
         <v>234</v>
       </c>
       <c r="B235">
-        <v>0.8322742870251417</v>
+        <v>0.8322742870251414</v>
       </c>
       <c r="C235">
         <v>0.7758966757825618</v>
       </c>
       <c r="D235">
-        <v>0.8568097147472645</v>
+        <v>0.8568097147472644</v>
       </c>
       <c r="E235">
         <v>0.9014744274813183</v>
@@ -4363,7 +4363,7 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>0.7785816758544635</v>
+        <v>0.7785816758544634</v>
       </c>
       <c r="C236">
         <v>0.7061247326290678</v>
@@ -4380,7 +4380,7 @@
         <v>236</v>
       </c>
       <c r="B237">
-        <v>0.8870535156547629</v>
+        <v>0.887053515654763</v>
       </c>
       <c r="C237">
         <v>0.8059656900073627</v>
@@ -4389,7 +4389,7 @@
         <v>0.8417164520553727</v>
       </c>
       <c r="E237">
-        <v>0.8647128396592253</v>
+        <v>0.8647128396592254</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4397,7 +4397,7 @@
         <v>237</v>
       </c>
       <c r="B238">
-        <v>0.9017484295438978</v>
+        <v>0.901748429543898</v>
       </c>
       <c r="C238">
         <v>0.8404159744790124</v>
@@ -4406,7 +4406,7 @@
         <v>0.8793038194342047</v>
       </c>
       <c r="E238">
-        <v>0.8999234831971353</v>
+        <v>0.8999234831971356</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4414,7 +4414,7 @@
         <v>238</v>
       </c>
       <c r="B239">
-        <v>0.8336107239542269</v>
+        <v>0.833610723954227</v>
       </c>
       <c r="C239">
         <v>0.7327556464920185</v>
@@ -4423,7 +4423,7 @@
         <v>0.765885641174325</v>
       </c>
       <c r="E239">
-        <v>0.7952264444067236</v>
+        <v>0.795226444406724</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4440,7 +4440,7 @@
         <v>0.6903781902372509</v>
       </c>
       <c r="E240">
-        <v>0.695967930868834</v>
+        <v>0.6959679308688339</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4465,7 +4465,7 @@
         <v>241</v>
       </c>
       <c r="B242">
-        <v>0.8689748227910361</v>
+        <v>0.8689748227910362</v>
       </c>
       <c r="C242">
         <v>0.8115127542183835</v>
@@ -4491,7 +4491,7 @@
         <v>0.9065388454283512</v>
       </c>
       <c r="E243">
-        <v>0.9326056608247526</v>
+        <v>0.9326056608247527</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4499,7 +4499,7 @@
         <v>243</v>
       </c>
       <c r="B244">
-        <v>0.8689748227910361</v>
+        <v>0.8689748227910364</v>
       </c>
       <c r="C244">
         <v>0.8115127542183835</v>
@@ -4533,13 +4533,13 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>0.7947651936036215</v>
+        <v>0.7947651936036214</v>
       </c>
       <c r="C246">
         <v>0.7424587516401921</v>
       </c>
       <c r="D246">
-        <v>0.808940734121872</v>
+        <v>0.8089407341218718</v>
       </c>
       <c r="E246">
         <v>0.8507239826460006</v>
@@ -4556,7 +4556,7 @@
         <v>0.742458751640192</v>
       </c>
       <c r="D247">
-        <v>0.808940734121872</v>
+        <v>0.8089407341218718</v>
       </c>
       <c r="E247">
         <v>0.8507239826460006</v>
@@ -4573,7 +4573,7 @@
         <v>0.7647484974324601</v>
       </c>
       <c r="D248">
-        <v>0.8249579810918912</v>
+        <v>0.8249579810918913</v>
       </c>
       <c r="E248">
         <v>0.8714064714767153</v>
@@ -4584,7 +4584,7 @@
         <v>248</v>
       </c>
       <c r="B249">
-        <v>0.7796154797839953</v>
+        <v>0.7796154797839954</v>
       </c>
       <c r="C249">
         <v>0.6685088936876817</v>
@@ -4604,7 +4604,7 @@
         <v>1.004033223074399</v>
       </c>
       <c r="C250">
-        <v>1.012327922311473</v>
+        <v>1.012327922311474</v>
       </c>
       <c r="D250">
         <v>1.117445210358976</v>
@@ -4635,10 +4635,10 @@
         <v>251</v>
       </c>
       <c r="B252">
-        <v>0.982492933249799</v>
+        <v>0.9824929332497989</v>
       </c>
       <c r="C252">
-        <v>0.9831297383359121</v>
+        <v>0.9831297383359122</v>
       </c>
       <c r="D252">
         <v>1.092307253453042</v>
@@ -4652,13 +4652,13 @@
         <v>252</v>
       </c>
       <c r="B253">
-        <v>0.8802832685375832</v>
+        <v>0.8802832685375831</v>
       </c>
       <c r="C253">
         <v>0.8503285767067928</v>
       </c>
       <c r="D253">
-        <v>0.9311527905021247</v>
+        <v>0.9311527905021248</v>
       </c>
       <c r="E253">
         <v>0.9377489252534309</v>
@@ -4692,7 +4692,7 @@
         <v>0.8503285767067927</v>
       </c>
       <c r="D255">
-        <v>0.9311527905021247</v>
+        <v>0.9311527905021248</v>
       </c>
       <c r="E255">
         <v>0.9377489252534309</v>
@@ -4703,16 +4703,16 @@
         <v>255</v>
       </c>
       <c r="B256">
-        <v>0.8281272463912501</v>
+        <v>0.8281272463912502</v>
       </c>
       <c r="C256">
         <v>0.7799567079564416</v>
       </c>
       <c r="D256">
-        <v>0.8798012294513611</v>
+        <v>0.8798012294513614</v>
       </c>
       <c r="E256">
-        <v>0.908213295940674</v>
+        <v>0.9082132959406739</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4723,10 +4723,10 @@
         <v>0.7310620366450946</v>
       </c>
       <c r="C257">
-        <v>0.6801972721296384</v>
+        <v>0.6801972721296385</v>
       </c>
       <c r="D257">
-        <v>0.7409984816072398</v>
+        <v>0.7409984816072399</v>
       </c>
       <c r="E257">
         <v>0.7580654318255579</v>
@@ -4740,7 +4740,7 @@
         <v>0.8179555217652814</v>
       </c>
       <c r="C258">
-        <v>0.7884743721357655</v>
+        <v>0.7884743721357658</v>
       </c>
       <c r="D258">
         <v>0.8300057939494145</v>
@@ -4757,7 +4757,7 @@
         <v>0.8179555217652813</v>
       </c>
       <c r="C259">
-        <v>0.7884743721357655</v>
+        <v>0.7884743721357657</v>
       </c>
       <c r="D259">
         <v>0.8300057939494144</v>
@@ -4774,10 +4774,10 @@
         <v>0.5227569614598798</v>
       </c>
       <c r="C260">
-        <v>0.4953207503491977</v>
+        <v>0.4953207503491978</v>
       </c>
       <c r="D260">
-        <v>0.4681145372297417</v>
+        <v>0.4681145372297416</v>
       </c>
       <c r="E260">
         <v>0.4062309844397247</v>
@@ -4791,7 +4791,7 @@
         <v>0.3510778643752695</v>
       </c>
       <c r="C261">
-        <v>0.3160022795961596</v>
+        <v>0.3160022795961597</v>
       </c>
       <c r="D261">
         <v>0.2893241320616493</v>
@@ -4811,10 +4811,10 @@
         <v>0.4843310701890298</v>
       </c>
       <c r="D262">
-        <v>0.4679087726285483</v>
+        <v>0.4679087726285484</v>
       </c>
       <c r="E262">
-        <v>0.4141243769942614</v>
+        <v>0.4141243769942613</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4825,13 +4825,13 @@
         <v>0.4832554658287297</v>
       </c>
       <c r="C263">
-        <v>0.4543730443091589</v>
+        <v>0.454373044309159</v>
       </c>
       <c r="D263">
         <v>0.4353618714114907</v>
       </c>
       <c r="E263">
-        <v>0.3917525336628399</v>
+        <v>0.3917525336628397</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -4842,7 +4842,7 @@
         <v>0.4421260001089494</v>
       </c>
       <c r="C264">
-        <v>0.4062794577950289</v>
+        <v>0.4062794577950291</v>
       </c>
       <c r="D264">
         <v>0.3989518436151622</v>
@@ -4856,13 +4856,13 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>0.4421260001089495</v>
+        <v>0.4421260001089494</v>
       </c>
       <c r="C265">
-        <v>0.4062794577950289</v>
+        <v>0.4062794577950291</v>
       </c>
       <c r="D265">
-        <v>0.3989518436151621</v>
+        <v>0.3989518436151622</v>
       </c>
       <c r="E265">
         <v>0.3653638112216108</v>
@@ -4876,7 +4876,7 @@
         <v>0.5561542066610559</v>
       </c>
       <c r="C266">
-        <v>0.5088255270260515</v>
+        <v>0.5088255270260517</v>
       </c>
       <c r="D266">
         <v>0.4691809798786742</v>
@@ -4893,7 +4893,7 @@
         <v>0.4421260001089495</v>
       </c>
       <c r="C267">
-        <v>0.4062794577950289</v>
+        <v>0.4062794577950291</v>
       </c>
       <c r="D267">
         <v>0.3989518436151622</v>
@@ -4910,7 +4910,7 @@
         <v>0.3510778643752695</v>
       </c>
       <c r="C268">
-        <v>0.3160022795961596</v>
+        <v>0.3160022795961597</v>
       </c>
       <c r="D268">
         <v>0.2893241320616493</v>
@@ -4927,7 +4927,7 @@
         <v>0.3510778643752695</v>
       </c>
       <c r="C269">
-        <v>0.3160022795961596</v>
+        <v>0.3160022795961597</v>
       </c>
       <c r="D269">
         <v>0.2893241320616494</v>
@@ -4944,7 +4944,7 @@
         <v>0.3834399307004618</v>
       </c>
       <c r="C270">
-        <v>0.3270528436720863</v>
+        <v>0.3270528436720864</v>
       </c>
       <c r="D270">
         <v>0.3008135266194772</v>
@@ -4958,7 +4958,7 @@
         <v>270</v>
       </c>
       <c r="B271">
-        <v>0.4072581397209273</v>
+        <v>0.4072581397209274</v>
       </c>
       <c r="C271">
         <v>0.3304266661339383</v>
@@ -4975,7 +4975,7 @@
         <v>271</v>
       </c>
       <c r="B272">
-        <v>0.4072581397209273</v>
+        <v>0.4072581397209274</v>
       </c>
       <c r="C272">
         <v>0.3304266661339383</v>
@@ -4995,10 +4995,10 @@
         <v>0.3913062294212122</v>
       </c>
       <c r="C273">
-        <v>0.3389340836547404</v>
+        <v>0.3389340836547405</v>
       </c>
       <c r="D273">
-        <v>0.3089025924499338</v>
+        <v>0.3089025924499337</v>
       </c>
       <c r="E273">
         <v>0.2721767786696517</v>
@@ -5012,7 +5012,7 @@
         <v>0.3913062294212122</v>
       </c>
       <c r="C274">
-        <v>0.3389340836547404</v>
+        <v>0.3389340836547405</v>
       </c>
       <c r="D274">
         <v>0.3089025924499337</v>
@@ -5083,10 +5083,10 @@
         <v>0.670522381047488</v>
       </c>
       <c r="D278">
-        <v>0.6907505413280068</v>
+        <v>0.6907505413280071</v>
       </c>
       <c r="E278">
-        <v>0.7080390846019662</v>
+        <v>0.7080390846019664</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5097,7 +5097,7 @@
         <v>0.7961357186318707</v>
       </c>
       <c r="C279">
-        <v>0.6949394984574163</v>
+        <v>0.6949394984574162</v>
       </c>
       <c r="D279">
         <v>0.7186404585886492</v>
@@ -5120,7 +5120,7 @@
         <v>0.7186404585886491</v>
       </c>
       <c r="E280">
-        <v>0.7240240076526753</v>
+        <v>0.7240240076526752</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5134,7 +5134,7 @@
         <v>0.3391747329549344</v>
       </c>
       <c r="D281">
-        <v>0.2813080996469888</v>
+        <v>0.2813080996469887</v>
       </c>
       <c r="E281">
         <v>0.2347468561296664</v>
@@ -5162,10 +5162,10 @@
         <v>282</v>
       </c>
       <c r="B283">
-        <v>0.4072606077729042</v>
+        <v>0.4072606077729041</v>
       </c>
       <c r="C283">
-        <v>0.3318050227177504</v>
+        <v>0.3318050227177505</v>
       </c>
       <c r="D283">
         <v>0.2998038512726432</v>
@@ -5202,10 +5202,10 @@
         <v>0.3624933192322065</v>
       </c>
       <c r="D285">
-        <v>0.3249749874692948</v>
+        <v>0.3249749874692947</v>
       </c>
       <c r="E285">
-        <v>0.296291604001718</v>
+        <v>0.2962916040017179</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5250,13 +5250,13 @@
         <v>0.5480792932946182</v>
       </c>
       <c r="C288">
-        <v>0.5394209843206541</v>
+        <v>0.5394209843206543</v>
       </c>
       <c r="D288">
         <v>0.5846923099107546</v>
       </c>
       <c r="E288">
-        <v>0.5943835276226762</v>
+        <v>0.5943835276226761</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5270,10 +5270,10 @@
         <v>0.8214459633199471</v>
       </c>
       <c r="D289">
-        <v>0.8503621348313321</v>
+        <v>0.8503621348313322</v>
       </c>
       <c r="E289">
-        <v>0.8100983657243221</v>
+        <v>0.8100983657243219</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5290,7 +5290,7 @@
         <v>0.7247592647149045</v>
       </c>
       <c r="E290">
-        <v>0.7084080068490993</v>
+        <v>0.7084080068490991</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5324,7 +5324,7 @@
         <v>0.6208908771626847</v>
       </c>
       <c r="E292">
-        <v>0.6329949246769533</v>
+        <v>0.6329949246769534</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5355,7 +5355,7 @@
         <v>0.5458192023581104</v>
       </c>
       <c r="D294">
-        <v>0.5818763838290529</v>
+        <v>0.581876383829053</v>
       </c>
       <c r="E294">
         <v>0.5911652004024788</v>
@@ -5372,7 +5372,7 @@
         <v>0.7918945732852581</v>
       </c>
       <c r="D295">
-        <v>0.8283639907887191</v>
+        <v>0.8283639907887193</v>
       </c>
       <c r="E295">
         <v>0.7956562232142852</v>
@@ -5389,10 +5389,10 @@
         <v>0.8397829372276504</v>
       </c>
       <c r="D296">
-        <v>0.894317909121183</v>
+        <v>0.8943179091211831</v>
       </c>
       <c r="E296">
-        <v>0.8642671504298245</v>
+        <v>0.8642671504298243</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5400,7 +5400,7 @@
         <v>296</v>
       </c>
       <c r="B297">
-        <v>0.7507443754621334</v>
+        <v>0.7507443754621335</v>
       </c>
       <c r="C297">
         <v>0.7470374738481502</v>
@@ -5409,7 +5409,7 @@
         <v>0.7977854862433041</v>
       </c>
       <c r="E297">
-        <v>0.7830715136146494</v>
+        <v>0.7830715136146493</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5417,13 +5417,13 @@
         <v>297</v>
       </c>
       <c r="B298">
-        <v>0.761833619087198</v>
+        <v>0.7618336190871983</v>
       </c>
       <c r="C298">
         <v>0.7788839875805723</v>
       </c>
       <c r="D298">
-        <v>0.8316766292984124</v>
+        <v>0.8316766292984126</v>
       </c>
       <c r="E298">
         <v>0.8057873927272737</v>
@@ -5443,7 +5443,7 @@
         <v>0.7440467108182638</v>
       </c>
       <c r="E299">
-        <v>0.729696993132513</v>
+        <v>0.7296969931325128</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5457,7 +5457,7 @@
         <v>0.7918945732852581</v>
       </c>
       <c r="D300">
-        <v>0.8283639907887191</v>
+        <v>0.8283639907887193</v>
       </c>
       <c r="E300">
         <v>0.795656223214285</v>
@@ -5477,7 +5477,7 @@
         <v>0.8329492789299824</v>
       </c>
       <c r="E301">
-        <v>0.8122553228986102</v>
+        <v>0.8122553228986101</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5502,7 +5502,7 @@
         <v>302</v>
       </c>
       <c r="B303">
-        <v>0.6446648353645992</v>
+        <v>0.6446648353645993</v>
       </c>
       <c r="C303">
         <v>0.5969958650235767</v>
@@ -5511,7 +5511,7 @@
         <v>0.6465730730438306</v>
       </c>
       <c r="E303">
-        <v>0.6515724639706755</v>
+        <v>0.6515724639706756</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>0.7074029040556606</v>
       </c>
       <c r="C304">
-        <v>0.6906220763809413</v>
+        <v>0.6906220763809414</v>
       </c>
       <c r="D304">
         <v>0.7037906162609155</v>
       </c>
       <c r="E304">
-        <v>0.6757988049712363</v>
+        <v>0.6757988049712362</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5542,7 +5542,7 @@
         <v>0.6906220763809413</v>
       </c>
       <c r="D305">
-        <v>0.7037906162609157</v>
+        <v>0.7037906162609158</v>
       </c>
       <c r="E305">
         <v>0.6757988049712363</v>
@@ -5553,16 +5553,16 @@
         <v>305</v>
       </c>
       <c r="B306">
-        <v>0.7480967884013628</v>
+        <v>0.748096788401363</v>
       </c>
       <c r="C306">
-        <v>0.7267892393016004</v>
+        <v>0.7267892393016006</v>
       </c>
       <c r="D306">
         <v>0.7219057604710902</v>
       </c>
       <c r="E306">
-        <v>0.6772140343107502</v>
+        <v>0.6772140343107503</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5587,13 +5587,13 @@
         <v>307</v>
       </c>
       <c r="B308">
-        <v>0.7056905456579801</v>
+        <v>0.70569054565798</v>
       </c>
       <c r="C308">
         <v>0.6755574348854892</v>
       </c>
       <c r="D308">
-        <v>0.664861318222531</v>
+        <v>0.6648613182225311</v>
       </c>
       <c r="E308">
         <v>0.6355298732368531</v>
@@ -5604,16 +5604,16 @@
         <v>308</v>
       </c>
       <c r="B309">
-        <v>0.7480967884013628</v>
+        <v>0.748096788401363</v>
       </c>
       <c r="C309">
-        <v>0.7267892393016004</v>
+        <v>0.7267892393016006</v>
       </c>
       <c r="D309">
         <v>0.7219057604710903</v>
       </c>
       <c r="E309">
-        <v>0.6772140343107502</v>
+        <v>0.6772140343107503</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5621,13 +5621,13 @@
         <v>309</v>
       </c>
       <c r="B310">
-        <v>0.6674569967773457</v>
+        <v>0.6674569967773456</v>
       </c>
       <c r="C310">
         <v>0.6378831375338511</v>
       </c>
       <c r="D310">
-        <v>0.6443476947543976</v>
+        <v>0.6443476947543977</v>
       </c>
       <c r="E310">
         <v>0.6313604635217952</v>
@@ -5644,7 +5644,7 @@
         <v>0.3856816658149778</v>
       </c>
       <c r="D311">
-        <v>0.348965506247833</v>
+        <v>0.3489655062478331</v>
       </c>
       <c r="E311">
         <v>0.3231679864523245</v>
@@ -5664,7 +5664,7 @@
         <v>0.3980596797253503</v>
       </c>
       <c r="E312">
-        <v>0.352447274275524</v>
+        <v>0.3524472742755241</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5678,7 +5678,7 @@
         <v>0.3856816658149778</v>
       </c>
       <c r="D313">
-        <v>0.348965506247833</v>
+        <v>0.3489655062478331</v>
       </c>
       <c r="E313">
         <v>0.3231679864523245</v>
@@ -5695,7 +5695,7 @@
         <v>0.3856816658149778</v>
       </c>
       <c r="D314">
-        <v>0.348965506247833</v>
+        <v>0.3489655062478331</v>
       </c>
       <c r="E314">
         <v>0.3231679864523245</v>
@@ -5831,7 +5831,7 @@
         <v>0.8661426189340904</v>
       </c>
       <c r="D322">
-        <v>0.915073563127501</v>
+        <v>0.9150735631275011</v>
       </c>
       <c r="E322">
         <v>0.873262833170359</v>
@@ -5879,7 +5879,7 @@
         <v>1.048657917385463</v>
       </c>
       <c r="C325">
-        <v>1.084798437657404</v>
+        <v>1.084798437657405</v>
       </c>
       <c r="D325">
         <v>1.129192835550934</v>
@@ -5896,7 +5896,7 @@
         <v>1.098675288796602</v>
       </c>
       <c r="C326">
-        <v>1.144622279306522</v>
+        <v>1.144622279306523</v>
       </c>
       <c r="D326">
         <v>1.187349683170435</v>
@@ -5913,13 +5913,13 @@
         <v>0.8758848584044689</v>
       </c>
       <c r="C327">
-        <v>0.8404261901087779</v>
+        <v>0.8404261901087781</v>
       </c>
       <c r="D327">
         <v>0.8207068186260917</v>
       </c>
       <c r="E327">
-        <v>0.7659881586582932</v>
+        <v>0.7659881586582933</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -5930,7 +5930,7 @@
         <v>0.8682150954089666</v>
       </c>
       <c r="C328">
-        <v>0.8069915490778515</v>
+        <v>0.8069915490778518</v>
       </c>
       <c r="D328">
         <v>0.7867951575244854</v>
@@ -5947,7 +5947,7 @@
         <v>0.8236638027714898</v>
       </c>
       <c r="C329">
-        <v>0.758247160390088</v>
+        <v>0.7582471603900881</v>
       </c>
       <c r="D329">
         <v>0.7268162462175723</v>
@@ -5961,16 +5961,16 @@
         <v>329</v>
       </c>
       <c r="B330">
-        <v>0.8682150954089666</v>
+        <v>0.8682150954089665</v>
       </c>
       <c r="C330">
-        <v>0.8069915490778515</v>
+        <v>0.8069915490778516</v>
       </c>
       <c r="D330">
         <v>0.7867951575244855</v>
       </c>
       <c r="E330">
-        <v>0.7283632443046714</v>
+        <v>0.7283632443046715</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5978,7 +5978,7 @@
         <v>330</v>
       </c>
       <c r="B331">
-        <v>0.9314513077284841</v>
+        <v>0.9314513077284842</v>
       </c>
       <c r="C331">
         <v>0.9032191210467738</v>
@@ -6004,7 +6004,7 @@
         <v>0.9001994514272916</v>
       </c>
       <c r="E332">
-        <v>0.8554415508730465</v>
+        <v>0.8554415508730467</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6015,13 +6015,13 @@
         <v>0.940316170668257</v>
       </c>
       <c r="C333">
-        <v>0.9667124728232703</v>
+        <v>0.9667124728232706</v>
       </c>
       <c r="D333">
         <v>1.022192547525694</v>
       </c>
       <c r="E333">
-        <v>0.9741763716825931</v>
+        <v>0.9741763716825933</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6035,10 +6035,10 @@
         <v>0.9599596969854894</v>
       </c>
       <c r="D334">
-        <v>0.9931309898614368</v>
+        <v>0.9931309898614369</v>
       </c>
       <c r="E334">
-        <v>0.9522777768487685</v>
+        <v>0.9522777768487686</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6049,10 +6049,10 @@
         <v>0.8781885374365169</v>
       </c>
       <c r="C335">
-        <v>0.891407386446463</v>
+        <v>0.8914073864464631</v>
       </c>
       <c r="D335">
-        <v>0.9246403648612905</v>
+        <v>0.9246403648612906</v>
       </c>
       <c r="E335">
         <v>0.8897883701632155</v>
@@ -6080,7 +6080,7 @@
         <v>336</v>
       </c>
       <c r="B337">
-        <v>0.5155200777747964</v>
+        <v>0.5155200777747962</v>
       </c>
       <c r="C337">
         <v>0.4565212221118385</v>
@@ -6089,7 +6089,7 @@
         <v>0.495984042583481</v>
       </c>
       <c r="E337">
-        <v>0.5559237529811617</v>
+        <v>0.5559237529811616</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6106,7 +6106,7 @@
         <v>0.5391066367462075</v>
       </c>
       <c r="E338">
-        <v>0.6332184658471748</v>
+        <v>0.6332184658471747</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6120,7 +6120,7 @@
         <v>0.4565212221118385</v>
       </c>
       <c r="D339">
-        <v>0.495984042583481</v>
+        <v>0.4959840425834811</v>
       </c>
       <c r="E339">
         <v>0.5559237529811617</v>
@@ -6131,7 +6131,7 @@
         <v>339</v>
       </c>
       <c r="B340">
-        <v>0.4223457384381161</v>
+        <v>0.4223457384381162</v>
       </c>
       <c r="C340">
         <v>0.3528784071593133</v>
@@ -6140,7 +6140,7 @@
         <v>0.3797456644586655</v>
       </c>
       <c r="E340">
-        <v>0.4345618973106103</v>
+        <v>0.4345618973106102</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,10 +6154,10 @@
         <v>0.37911258768813</v>
       </c>
       <c r="D341">
-        <v>0.4088107629812271</v>
+        <v>0.4088107629812272</v>
       </c>
       <c r="E341">
-        <v>0.470208566264101</v>
+        <v>0.4702085662641009</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6174,7 +6174,7 @@
         <v>0.4055557063756077</v>
       </c>
       <c r="E342">
-        <v>0.4721802028821035</v>
+        <v>0.4721802028821034</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6208,7 +6208,7 @@
         <v>0.3797456644586655</v>
       </c>
       <c r="E344">
-        <v>0.4345618973106103</v>
+        <v>0.4345618973106102</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6242,7 +6242,7 @@
         <v>0.2755603983053457</v>
       </c>
       <c r="E346">
-        <v>0.310427198350539</v>
+        <v>0.3104271983505389</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6290,7 +6290,7 @@
         <v>0.433972537257714</v>
       </c>
       <c r="D349">
-        <v>0.4168481035505135</v>
+        <v>0.4168481035505134</v>
       </c>
       <c r="E349">
         <v>0.4341119334078969</v>
@@ -6457,7 +6457,7 @@
         <v>0.2582705763467728</v>
       </c>
       <c r="C359">
-        <v>0.2072313160590197</v>
+        <v>0.2072313160590198</v>
       </c>
       <c r="D359">
         <v>0.2179926656601302</v>
@@ -6474,7 +6474,7 @@
         <v>0.2582705763467728</v>
       </c>
       <c r="C360">
-        <v>0.2072313160590197</v>
+        <v>0.2072313160590198</v>
       </c>
       <c r="D360">
         <v>0.2179926656601302</v>
@@ -6491,10 +6491,10 @@
         <v>0.632172966290414</v>
       </c>
       <c r="C361">
-        <v>0.5928078228962116</v>
+        <v>0.5928078228962117</v>
       </c>
       <c r="D361">
-        <v>0.6500125620182865</v>
+        <v>0.6500125620182866</v>
       </c>
       <c r="E361">
         <v>0.6823989311186407</v>
@@ -6514,7 +6514,7 @@
         <v>0.4637272086406405</v>
       </c>
       <c r="E362">
-        <v>0.4757822276139663</v>
+        <v>0.4757822276139664</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6542,13 +6542,13 @@
         <v>0.6721013264557354</v>
       </c>
       <c r="C364">
-        <v>0.6269233962431804</v>
+        <v>0.6269233962431806</v>
       </c>
       <c r="D364">
-        <v>0.6859738685423968</v>
+        <v>0.6859738685423967</v>
       </c>
       <c r="E364">
-        <v>0.6756325048024987</v>
+        <v>0.6756325048024988</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6559,13 +6559,13 @@
         <v>0.6721013264557354</v>
       </c>
       <c r="C365">
-        <v>0.6269233962431804</v>
+        <v>0.6269233962431806</v>
       </c>
       <c r="D365">
         <v>0.6859738685423967</v>
       </c>
       <c r="E365">
-        <v>0.6756325048024987</v>
+        <v>0.6756325048024988</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6576,13 +6576,13 @@
         <v>0.537490310786539</v>
       </c>
       <c r="C366">
-        <v>0.4719731644752242</v>
+        <v>0.4719731644752243</v>
       </c>
       <c r="D366">
-        <v>0.4721609036382022</v>
+        <v>0.4721609036382021</v>
       </c>
       <c r="E366">
-        <v>0.4593196743277891</v>
+        <v>0.4593196743277893</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6590,16 +6590,16 @@
         <v>366</v>
       </c>
       <c r="B367">
-        <v>0.5374903107865391</v>
+        <v>0.537490310786539</v>
       </c>
       <c r="C367">
-        <v>0.4719731644752242</v>
+        <v>0.4719731644752243</v>
       </c>
       <c r="D367">
-        <v>0.4721609036382022</v>
+        <v>0.4721609036382021</v>
       </c>
       <c r="E367">
-        <v>0.4593196743277891</v>
+        <v>0.4593196743277893</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6610,7 +6610,7 @@
         <v>0.6413324968384434</v>
       </c>
       <c r="C368">
-        <v>0.5866422856179698</v>
+        <v>0.5866422856179697</v>
       </c>
       <c r="D368">
         <v>0.6113104557010394</v>
@@ -6627,13 +6627,13 @@
         <v>0.537490310786539</v>
       </c>
       <c r="C369">
-        <v>0.4719731644752242</v>
+        <v>0.4719731644752243</v>
       </c>
       <c r="D369">
         <v>0.4721609036382021</v>
       </c>
       <c r="E369">
-        <v>0.4593196743277892</v>
+        <v>0.4593196743277893</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6675,7 +6675,7 @@
         <v>371</v>
       </c>
       <c r="B372">
-        <v>0.5151138412663395</v>
+        <v>0.5151138412663394</v>
       </c>
       <c r="C372">
         <v>0.4225120702085022</v>
@@ -6692,16 +6692,16 @@
         <v>372</v>
       </c>
       <c r="B373">
-        <v>0.6592528191782039</v>
+        <v>0.6592528191782038</v>
       </c>
       <c r="C373">
         <v>0.6023531556828773</v>
       </c>
       <c r="D373">
-        <v>0.6572050281261411</v>
+        <v>0.6572050281261412</v>
       </c>
       <c r="E373">
-        <v>0.7082872820273931</v>
+        <v>0.708287282027393</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6712,13 +6712,13 @@
         <v>0.5518100893351012</v>
       </c>
       <c r="C374">
-        <v>0.4928426463986852</v>
+        <v>0.4928426463986854</v>
       </c>
       <c r="D374">
-        <v>0.525757798697297</v>
+        <v>0.5257577986972969</v>
       </c>
       <c r="E374">
-        <v>0.5689016148468827</v>
+        <v>0.5689016148468826</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6729,13 +6729,13 @@
         <v>0.6380705101361434</v>
       </c>
       <c r="C375">
-        <v>0.5633156256975421</v>
+        <v>0.5633156256975422</v>
       </c>
       <c r="D375">
         <v>0.6182504887335911</v>
       </c>
       <c r="E375">
-        <v>0.6642552290275532</v>
+        <v>0.6642552290275531</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6746,13 +6746,13 @@
         <v>0.5376706406589783</v>
       </c>
       <c r="C376">
-        <v>0.4615991457513071</v>
+        <v>0.4615991457513073</v>
       </c>
       <c r="D376">
-        <v>0.491889069570336</v>
+        <v>0.4918890695703358</v>
       </c>
       <c r="E376">
-        <v>0.5309070385163907</v>
+        <v>0.5309070385163905</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6763,13 +6763,13 @@
         <v>0.5376706406589783</v>
       </c>
       <c r="C377">
-        <v>0.4615991457513071</v>
+        <v>0.4615991457513072</v>
       </c>
       <c r="D377">
-        <v>0.491889069570336</v>
+        <v>0.4918890695703358</v>
       </c>
       <c r="E377">
-        <v>0.5309070385163905</v>
+        <v>0.5309070385163904</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6786,7 +6786,7 @@
         <v>0.7527793955253977</v>
       </c>
       <c r="E378">
-        <v>0.7767431948250509</v>
+        <v>0.7767431948250507</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -6803,7 +6803,7 @@
         <v>0.7527793955253976</v>
       </c>
       <c r="E379">
-        <v>0.7767431948250509</v>
+        <v>0.7767431948250507</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -6817,10 +6817,10 @@
         <v>0.6584028586315555</v>
       </c>
       <c r="D380">
-        <v>0.7104586669103778</v>
+        <v>0.710458666910378</v>
       </c>
       <c r="E380">
-        <v>0.7323092097192727</v>
+        <v>0.7323092097192726</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6834,10 +6834,10 @@
         <v>0.6584028586315555</v>
       </c>
       <c r="D381">
-        <v>0.7104586669103778</v>
+        <v>0.710458666910378</v>
       </c>
       <c r="E381">
-        <v>0.7323092097192727</v>
+        <v>0.7323092097192725</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,7 +6848,7 @@
         <v>0.7112014173718876</v>
       </c>
       <c r="C382">
-        <v>0.6141710539190596</v>
+        <v>0.6141710539190597</v>
       </c>
       <c r="D382">
         <v>0.6169278996928496</v>
@@ -6879,16 +6879,16 @@
         <v>383</v>
       </c>
       <c r="B384">
-        <v>0.5727623777359058</v>
+        <v>0.5727623777359059</v>
       </c>
       <c r="C384">
         <v>0.5048149762963684</v>
       </c>
       <c r="D384">
-        <v>0.5567102127416605</v>
+        <v>0.5567102127416607</v>
       </c>
       <c r="E384">
-        <v>0.6052027618823187</v>
+        <v>0.6052027618823186</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6899,13 +6899,13 @@
         <v>0.7122519927323606</v>
       </c>
       <c r="C385">
-        <v>0.6584139019916906</v>
+        <v>0.6584139019916907</v>
       </c>
       <c r="D385">
         <v>0.7394239689319489</v>
       </c>
       <c r="E385">
-        <v>0.7645763773664009</v>
+        <v>0.7645763773664007</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6916,13 +6916,13 @@
         <v>0.4088043289849636</v>
       </c>
       <c r="C386">
-        <v>0.3545357846427462</v>
+        <v>0.3545357846427463</v>
       </c>
       <c r="D386">
         <v>0.3953094460260753</v>
       </c>
       <c r="E386">
-        <v>0.4367040995444147</v>
+        <v>0.4367040995444145</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6933,13 +6933,13 @@
         <v>0.4088043289849636</v>
       </c>
       <c r="C387">
-        <v>0.3545357846427462</v>
+        <v>0.3545357846427463</v>
       </c>
       <c r="D387">
         <v>0.3953094460260753</v>
       </c>
       <c r="E387">
-        <v>0.4367040995444146</v>
+        <v>0.4367040995444145</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6967,13 +6967,13 @@
         <v>0.6153096040526134</v>
       </c>
       <c r="C389">
-        <v>0.5196045992054685</v>
+        <v>0.5196045992054686</v>
       </c>
       <c r="D389">
         <v>0.4410149964765901</v>
       </c>
       <c r="E389">
-        <v>0.3602087524349145</v>
+        <v>0.3602087524349144</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6998,7 +6998,7 @@
         <v>390</v>
       </c>
       <c r="B391">
-        <v>0.7346819114259908</v>
+        <v>0.7346819114259907</v>
       </c>
       <c r="C391">
         <v>0.6401857876178613</v>
@@ -7024,7 +7024,7 @@
         <v>0.4410149964765901</v>
       </c>
       <c r="E392">
-        <v>0.3602087524349145</v>
+        <v>0.3602087524349144</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7032,7 +7032,7 @@
         <v>392</v>
       </c>
       <c r="B393">
-        <v>0.5195403607954792</v>
+        <v>0.5195403607954789</v>
       </c>
       <c r="C393">
         <v>0.4344126727139533</v>
@@ -7072,7 +7072,7 @@
         <v>0.446080888225621</v>
       </c>
       <c r="D395">
-        <v>0.3736005318333034</v>
+        <v>0.3736005318333033</v>
       </c>
       <c r="E395">
         <v>0.3021644985914662</v>
@@ -7086,7 +7086,7 @@
         <v>0.535893119534034</v>
       </c>
       <c r="C396">
-        <v>0.4460808882256209</v>
+        <v>0.446080888225621</v>
       </c>
       <c r="D396">
         <v>0.3736005318333034</v>
@@ -7100,7 +7100,7 @@
         <v>396</v>
       </c>
       <c r="B397">
-        <v>0.7265578095650893</v>
+        <v>0.7265578095650892</v>
       </c>
       <c r="C397">
         <v>0.6163415728498873</v>
@@ -7151,7 +7151,7 @@
         <v>399</v>
       </c>
       <c r="B400">
-        <v>0.5362152807526197</v>
+        <v>0.5362152807526198</v>
       </c>
       <c r="C400">
         <v>0.456515335834466</v>
@@ -7222,10 +7222,10 @@
         <v>0.4887787862105818</v>
       </c>
       <c r="C404">
-        <v>0.415242648395065</v>
+        <v>0.4152426483950649</v>
       </c>
       <c r="D404">
-        <v>0.3339863691758856</v>
+        <v>0.3339863691758855</v>
       </c>
       <c r="E404">
         <v>0.2443012515652587</v>
@@ -7239,7 +7239,7 @@
         <v>0.4887787862105817</v>
       </c>
       <c r="C405">
-        <v>0.415242648395065</v>
+        <v>0.4152426483950649</v>
       </c>
       <c r="D405">
         <v>0.3339863691758855</v>
@@ -7259,10 +7259,10 @@
         <v>0.415242648395065</v>
       </c>
       <c r="D406">
-        <v>0.3339863691758856</v>
+        <v>0.3339863691758855</v>
       </c>
       <c r="E406">
-        <v>0.2443012515652586</v>
+        <v>0.2443012515652587</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7290,7 +7290,7 @@
         <v>0.4448985697040225</v>
       </c>
       <c r="C408">
-        <v>0.3786566794725443</v>
+        <v>0.3786566794725442</v>
       </c>
       <c r="D408">
         <v>0.3077254157468584</v>
@@ -7321,10 +7321,10 @@
         <v>409</v>
       </c>
       <c r="B410">
-        <v>0.6467975496215469</v>
+        <v>0.646797549621547</v>
       </c>
       <c r="C410">
-        <v>0.5860978014463983</v>
+        <v>0.5860978014463984</v>
       </c>
       <c r="D410">
         <v>0.5814456456558292</v>
@@ -7344,7 +7344,7 @@
         <v>0.4792370791486901</v>
       </c>
       <c r="D411">
-        <v>0.4769161462849559</v>
+        <v>0.4769161462849558</v>
       </c>
       <c r="E411">
         <v>0.4518487295270212</v>
@@ -7361,7 +7361,7 @@
         <v>0.4792370791486901</v>
       </c>
       <c r="D412">
-        <v>0.4769161462849559</v>
+        <v>0.4769161462849558</v>
       </c>
       <c r="E412">
         <v>0.4518487295270212</v>
@@ -7378,7 +7378,7 @@
         <v>0.4055189445484124</v>
       </c>
       <c r="D413">
-        <v>0.3654592267230762</v>
+        <v>0.3654592267230761</v>
       </c>
       <c r="E413">
         <v>0.3271256714728488</v>
@@ -7389,7 +7389,7 @@
         <v>413</v>
       </c>
       <c r="B414">
-        <v>0.6212339930337659</v>
+        <v>0.621233993033766</v>
       </c>
       <c r="C414">
         <v>0.5469202443815013</v>
@@ -7409,7 +7409,7 @@
         <v>0.6247696649519519</v>
       </c>
       <c r="C415">
-        <v>0.5462986250751302</v>
+        <v>0.5462986250751301</v>
       </c>
       <c r="D415">
         <v>0.5083686334334181</v>
@@ -7440,16 +7440,16 @@
         <v>416</v>
       </c>
       <c r="B417">
-        <v>0.5840183854605979</v>
+        <v>0.5840183854605978</v>
       </c>
       <c r="C417">
-        <v>0.4983469835876999</v>
+        <v>0.4983469835876998</v>
       </c>
       <c r="D417">
-        <v>0.4144634619114105</v>
+        <v>0.4144634619114104</v>
       </c>
       <c r="E417">
-        <v>0.3309904789290185</v>
+        <v>0.3309904789290184</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7457,16 +7457,16 @@
         <v>417</v>
       </c>
       <c r="B418">
-        <v>0.5840183854605979</v>
+        <v>0.5840183854605978</v>
       </c>
       <c r="C418">
-        <v>0.4983469835876999</v>
+        <v>0.4983469835876998</v>
       </c>
       <c r="D418">
-        <v>0.4144634619114105</v>
+        <v>0.4144634619114104</v>
       </c>
       <c r="E418">
-        <v>0.3309904789290185</v>
+        <v>0.3309904789290184</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7474,10 +7474,10 @@
         <v>418</v>
       </c>
       <c r="B419">
-        <v>0.6205843309040393</v>
+        <v>0.6205843309040392</v>
       </c>
       <c r="C419">
-        <v>0.5616132390406136</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D419">
         <v>0.535416743769153</v>
@@ -7494,10 +7494,10 @@
         <v>0.6205843309040393</v>
       </c>
       <c r="C420">
-        <v>0.5616132390406136</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D420">
-        <v>0.5354167437691528</v>
+        <v>0.5354167437691529</v>
       </c>
       <c r="E420">
         <v>0.5019352301324375</v>
@@ -7508,10 +7508,10 @@
         <v>420</v>
       </c>
       <c r="B421">
-        <v>0.6455816928407861</v>
+        <v>0.645581692840786</v>
       </c>
       <c r="C421">
-        <v>0.5942463855431195</v>
+        <v>0.5942463855431196</v>
       </c>
       <c r="D421">
         <v>0.5750998084459027</v>
@@ -7528,7 +7528,7 @@
         <v>0.6455816928407861</v>
       </c>
       <c r="C422">
-        <v>0.5942463855431195</v>
+        <v>0.5942463855431196</v>
       </c>
       <c r="D422">
         <v>0.5750998084459028</v>
@@ -7545,10 +7545,10 @@
         <v>0.6205843309040393</v>
       </c>
       <c r="C423">
-        <v>0.5616132390406136</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D423">
-        <v>0.5354167437691529</v>
+        <v>0.535416743769153</v>
       </c>
       <c r="E423">
         <v>0.5019352301324375</v>
@@ -7562,10 +7562,10 @@
         <v>0.6205843309040393</v>
       </c>
       <c r="C424">
-        <v>0.5616132390406136</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D424">
-        <v>0.5354167437691529</v>
+        <v>0.5354167437691528</v>
       </c>
       <c r="E424">
         <v>0.5019352301324375</v>
@@ -7579,7 +7579,7 @@
         <v>0.6455816928407861</v>
       </c>
       <c r="C425">
-        <v>0.5942463855431195</v>
+        <v>0.5942463855431196</v>
       </c>
       <c r="D425">
         <v>0.5750998084459027</v>
@@ -7593,16 +7593,16 @@
         <v>425</v>
       </c>
       <c r="B426">
-        <v>0.6205843309040393</v>
+        <v>0.6205843309040392</v>
       </c>
       <c r="C426">
-        <v>0.5616132390406136</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D426">
         <v>0.5354167437691529</v>
       </c>
       <c r="E426">
-        <v>0.5019352301324373</v>
+        <v>0.5019352301324375</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -7613,7 +7613,7 @@
         <v>0.6015004762004682</v>
       </c>
       <c r="C427">
-        <v>0.5266241306780893</v>
+        <v>0.5266241306780896</v>
       </c>
       <c r="D427">
         <v>0.5025341597970742</v>
@@ -7630,7 +7630,7 @@
         <v>0.6015004762004681</v>
       </c>
       <c r="C428">
-        <v>0.5266241306780893</v>
+        <v>0.5266241306780894</v>
       </c>
       <c r="D428">
         <v>0.5025341597970743</v>
@@ -7644,13 +7644,13 @@
         <v>428</v>
       </c>
       <c r="B429">
-        <v>0.6205843309040393</v>
+        <v>0.6205843309040392</v>
       </c>
       <c r="C429">
-        <v>0.5616132390406136</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D429">
-        <v>0.5354167437691529</v>
+        <v>0.5354167437691528</v>
       </c>
       <c r="E429">
         <v>0.5019352301324375</v>
@@ -7664,7 +7664,7 @@
         <v>0.6205843309040393</v>
       </c>
       <c r="C430">
-        <v>0.5616132390406136</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D430">
         <v>0.535416743769153</v>
@@ -7715,10 +7715,10 @@
         <v>0.6205843309040392</v>
       </c>
       <c r="C433">
-        <v>0.5616132390406136</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D433">
-        <v>0.5354167437691529</v>
+        <v>0.5354167437691528</v>
       </c>
       <c r="E433">
         <v>0.5019352301324375</v>
@@ -7735,7 +7735,7 @@
         <v>0.524038092874927</v>
       </c>
       <c r="D434">
-        <v>0.4616323631462164</v>
+        <v>0.4616323631462163</v>
       </c>
       <c r="E434">
         <v>0.4123443633095357</v>
@@ -7749,10 +7749,10 @@
         <v>0.6205843309040393</v>
       </c>
       <c r="C435">
-        <v>0.5616132390406134</v>
+        <v>0.5616132390406137</v>
       </c>
       <c r="D435">
-        <v>0.5354167437691529</v>
+        <v>0.5354167437691528</v>
       </c>
       <c r="E435">
         <v>0.5019352301324375</v>
@@ -7766,13 +7766,13 @@
         <v>0.5704179546032245</v>
       </c>
       <c r="C436">
-        <v>0.4748004628206139</v>
+        <v>0.474800462820614</v>
       </c>
       <c r="D436">
         <v>0.3825122998512662</v>
       </c>
       <c r="E436">
-        <v>0.3049463499045429</v>
+        <v>0.304946349904543</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7780,16 +7780,16 @@
         <v>436</v>
       </c>
       <c r="B437">
-        <v>0.4395302218645256</v>
+        <v>0.4395302218645255</v>
       </c>
       <c r="C437">
         <v>0.3701275184104942</v>
       </c>
       <c r="D437">
-        <v>0.3327613330300143</v>
+        <v>0.3327613330300144</v>
       </c>
       <c r="E437">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7797,7 +7797,7 @@
         <v>437</v>
       </c>
       <c r="B438">
-        <v>0.4395302218645256</v>
+        <v>0.4395302218645255</v>
       </c>
       <c r="C438">
         <v>0.3701275184104942</v>
@@ -7806,7 +7806,7 @@
         <v>0.3327613330300143</v>
       </c>
       <c r="E438">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7814,16 +7814,16 @@
         <v>438</v>
       </c>
       <c r="B439">
-        <v>0.4395302218645256</v>
+        <v>0.4395302218645255</v>
       </c>
       <c r="C439">
         <v>0.3701275184104942</v>
       </c>
       <c r="D439">
-        <v>0.3327613330300143</v>
+        <v>0.3327613330300144</v>
       </c>
       <c r="E439">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7837,10 +7837,10 @@
         <v>0.3701275184104942</v>
       </c>
       <c r="D440">
-        <v>0.3327613330300143</v>
+        <v>0.3327613330300144</v>
       </c>
       <c r="E440">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7854,10 +7854,10 @@
         <v>0.3701275184104942</v>
       </c>
       <c r="D441">
-        <v>0.3327613330300143</v>
+        <v>0.3327613330300144</v>
       </c>
       <c r="E441">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7865,7 +7865,7 @@
         <v>441</v>
       </c>
       <c r="B442">
-        <v>0.4492549147231804</v>
+        <v>0.4492549147231803</v>
       </c>
       <c r="C442">
         <v>0.3809523827278488</v>
@@ -7885,13 +7885,13 @@
         <v>0.4395302218645255</v>
       </c>
       <c r="C443">
-        <v>0.3701275184104941</v>
+        <v>0.3701275184104942</v>
       </c>
       <c r="D443">
-        <v>0.3327613330300143</v>
+        <v>0.3327613330300144</v>
       </c>
       <c r="E443">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7899,16 +7899,16 @@
         <v>443</v>
       </c>
       <c r="B444">
-        <v>0.4395302218645256</v>
+        <v>0.4395302218645255</v>
       </c>
       <c r="C444">
         <v>0.3701275184104942</v>
       </c>
       <c r="D444">
-        <v>0.3327613330300143</v>
+        <v>0.3327613330300144</v>
       </c>
       <c r="E444">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7922,10 +7922,10 @@
         <v>0.3701275184104942</v>
       </c>
       <c r="D445">
-        <v>0.3327613330300143</v>
+        <v>0.3327613330300144</v>
       </c>
       <c r="E445">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7933,7 +7933,7 @@
         <v>445</v>
       </c>
       <c r="B446">
-        <v>0.4395302218645256</v>
+        <v>0.4395302218645255</v>
       </c>
       <c r="C446">
         <v>0.3701275184104942</v>
@@ -7942,7 +7942,7 @@
         <v>0.3327613330300143</v>
       </c>
       <c r="E446">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7956,10 +7956,10 @@
         <v>0.3701275184104942</v>
       </c>
       <c r="D447">
-        <v>0.3327613330300143</v>
+        <v>0.3327613330300144</v>
       </c>
       <c r="E447">
-        <v>0.3084643310789611</v>
+        <v>0.3084643310789612</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7970,13 +7970,13 @@
         <v>0.7388722972159346</v>
       </c>
       <c r="C448">
-        <v>0.6583289115128274</v>
+        <v>0.6583289115128275</v>
       </c>
       <c r="D448">
-        <v>0.5971628921244762</v>
+        <v>0.5971628921244763</v>
       </c>
       <c r="E448">
-        <v>0.5399546756098255</v>
+        <v>0.5399546756098256</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7987,7 +7987,7 @@
         <v>0.7388722972159346</v>
       </c>
       <c r="C449">
-        <v>0.6583289115128274</v>
+        <v>0.6583289115128275</v>
       </c>
       <c r="D449">
         <v>0.5971628921244762</v>
@@ -8004,10 +8004,10 @@
         <v>0.7388722972159346</v>
       </c>
       <c r="C450">
-        <v>0.6583289115128274</v>
+        <v>0.6583289115128275</v>
       </c>
       <c r="D450">
-        <v>0.5971628921244762</v>
+        <v>0.5971628921244763</v>
       </c>
       <c r="E450">
         <v>0.5399546756098256</v>
@@ -8021,13 +8021,13 @@
         <v>0.7388722972159346</v>
       </c>
       <c r="C451">
-        <v>0.6583289115128274</v>
+        <v>0.6583289115128275</v>
       </c>
       <c r="D451">
-        <v>0.5971628921244762</v>
+        <v>0.5971628921244763</v>
       </c>
       <c r="E451">
-        <v>0.5399546756098255</v>
+        <v>0.5399546756098256</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8038,10 +8038,10 @@
         <v>0.7388722972159345</v>
       </c>
       <c r="C452">
-        <v>0.6583289115128274</v>
+        <v>0.6583289115128275</v>
       </c>
       <c r="D452">
-        <v>0.5971628921244762</v>
+        <v>0.5971628921244763</v>
       </c>
       <c r="E452">
         <v>0.5399546756098256</v>
@@ -8055,10 +8055,10 @@
         <v>0.7388722972159346</v>
       </c>
       <c r="C453">
-        <v>0.6583289115128274</v>
+        <v>0.6583289115128275</v>
       </c>
       <c r="D453">
-        <v>0.5971628921244762</v>
+        <v>0.5971628921244763</v>
       </c>
       <c r="E453">
         <v>0.5399546756098256</v>
@@ -8092,7 +8092,7 @@
         <v>0.5091454602891847</v>
       </c>
       <c r="D455">
-        <v>0.4971147045156605</v>
+        <v>0.4971147045156606</v>
       </c>
       <c r="E455">
         <v>0.478261952889477</v>
@@ -8109,7 +8109,7 @@
         <v>0.5091454602891847</v>
       </c>
       <c r="D456">
-        <v>0.4971147045156605</v>
+        <v>0.4971147045156606</v>
       </c>
       <c r="E456">
         <v>0.478261952889477</v>
@@ -8126,10 +8126,10 @@
         <v>0.5091454602891847</v>
       </c>
       <c r="D457">
-        <v>0.4971147045156605</v>
+        <v>0.4971147045156606</v>
       </c>
       <c r="E457">
-        <v>0.4782619528894769</v>
+        <v>0.478261952889477</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8160,10 +8160,10 @@
         <v>0.5091454602891846</v>
       </c>
       <c r="D459">
-        <v>0.4971147045156605</v>
+        <v>0.4971147045156606</v>
       </c>
       <c r="E459">
-        <v>0.4782619528894769</v>
+        <v>0.478261952889477</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8177,10 +8177,10 @@
         <v>0.5091454602891847</v>
       </c>
       <c r="D460">
-        <v>0.4971147045156605</v>
+        <v>0.4971147045156606</v>
       </c>
       <c r="E460">
-        <v>0.4782619528894769</v>
+        <v>0.478261952889477</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8194,10 +8194,10 @@
         <v>0.5091454602891847</v>
       </c>
       <c r="D461">
-        <v>0.4971147045156605</v>
+        <v>0.4971147045156606</v>
       </c>
       <c r="E461">
-        <v>0.4782619528894769</v>
+        <v>0.478261952889477</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8211,7 +8211,7 @@
         <v>0.5091454602891847</v>
       </c>
       <c r="D462">
-        <v>0.4971147045156605</v>
+        <v>0.4971147045156606</v>
       </c>
       <c r="E462">
         <v>0.478261952889477</v>
@@ -8225,7 +8225,7 @@
         <v>0.6015004762004682</v>
       </c>
       <c r="C463">
-        <v>0.5266241306780893</v>
+        <v>0.5266241306780894</v>
       </c>
       <c r="D463">
         <v>0.5025341597970742</v>
@@ -8242,7 +8242,7 @@
         <v>0.6015004762004681</v>
       </c>
       <c r="C464">
-        <v>0.5266241306780894</v>
+        <v>0.5266241306780896</v>
       </c>
       <c r="D464">
         <v>0.5025341597970742</v>
@@ -8262,7 +8262,7 @@
         <v>0.524038092874927</v>
       </c>
       <c r="D465">
-        <v>0.4616323631462164</v>
+        <v>0.4616323631462163</v>
       </c>
       <c r="E465">
         <v>0.4123443633095357</v>
@@ -8279,10 +8279,10 @@
         <v>0.502364664721319</v>
       </c>
       <c r="D466">
-        <v>0.4407833649069365</v>
+        <v>0.4407833649069364</v>
       </c>
       <c r="E466">
-        <v>0.3890811579444478</v>
+        <v>0.3890811579444479</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8290,7 +8290,7 @@
         <v>466</v>
       </c>
       <c r="B467">
-        <v>0.6015004762004682</v>
+        <v>0.6015004762004681</v>
       </c>
       <c r="C467">
         <v>0.5266241306780894</v>
@@ -8313,7 +8313,7 @@
         <v>0.6583289115128275</v>
       </c>
       <c r="D468">
-        <v>0.5971628921244762</v>
+        <v>0.5971628921244763</v>
       </c>
       <c r="E468">
         <v>0.5399546756098256</v>
@@ -8327,13 +8327,13 @@
         <v>0.7388722972159347</v>
       </c>
       <c r="C469">
-        <v>0.6583289115128274</v>
+        <v>0.6583289115128275</v>
       </c>
       <c r="D469">
         <v>0.5971628921244763</v>
       </c>
       <c r="E469">
-        <v>0.5399546756098255</v>
+        <v>0.5399546756098256</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8344,10 +8344,10 @@
         <v>0.7388722972159347</v>
       </c>
       <c r="C470">
-        <v>0.6583289115128274</v>
+        <v>0.6583289115128275</v>
       </c>
       <c r="D470">
-        <v>0.5971628921244762</v>
+        <v>0.5971628921244763</v>
       </c>
       <c r="E470">
         <v>0.5399546756098256</v>
@@ -8361,7 +8361,7 @@
         <v>0.6015004762004682</v>
       </c>
       <c r="C471">
-        <v>0.5266241306780894</v>
+        <v>0.5266241306780896</v>
       </c>
       <c r="D471">
         <v>0.5025341597970743</v>
@@ -8381,7 +8381,7 @@
         <v>0.5091454602891847</v>
       </c>
       <c r="D472">
-        <v>0.4971147045156605</v>
+        <v>0.4971147045156606</v>
       </c>
       <c r="E472">
         <v>0.478261952889477</v>
@@ -8398,10 +8398,10 @@
         <v>0.502364664721319</v>
       </c>
       <c r="D473">
-        <v>0.4407833649069365</v>
+        <v>0.4407833649069364</v>
       </c>
       <c r="E473">
-        <v>0.3890811579444478</v>
+        <v>0.3890811579444479</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8415,10 +8415,10 @@
         <v>0.502364664721319</v>
       </c>
       <c r="D474">
-        <v>0.4407833649069364</v>
+        <v>0.4407833649069363</v>
       </c>
       <c r="E474">
-        <v>0.3890811579444477</v>
+        <v>0.3890811579444478</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8426,16 +8426,16 @@
         <v>474</v>
       </c>
       <c r="B475">
-        <v>0.5704179546032244</v>
+        <v>0.5704179546032245</v>
       </c>
       <c r="C475">
         <v>0.4748004628206139</v>
       </c>
       <c r="D475">
-        <v>0.3825122998512663</v>
+        <v>0.3825122998512662</v>
       </c>
       <c r="E475">
-        <v>0.3049463499045429</v>
+        <v>0.304946349904543</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8446,7 +8446,7 @@
         <v>0.433108021852545</v>
       </c>
       <c r="C476">
-        <v>0.3745007487187507</v>
+        <v>0.3745007487187508</v>
       </c>
       <c r="D476">
         <v>0.3432896963391412</v>
@@ -8460,7 +8460,7 @@
         <v>476</v>
       </c>
       <c r="B477">
-        <v>0.433108021852545</v>
+        <v>0.4331080218525449</v>
       </c>
       <c r="C477">
         <v>0.3745007487187507</v>
@@ -8494,7 +8494,7 @@
         <v>478</v>
       </c>
       <c r="B479">
-        <v>0.7885417921909125</v>
+        <v>0.7885417921909124</v>
       </c>
       <c r="C479">
         <v>0.6734618174260889</v>
@@ -8520,7 +8520,7 @@
         <v>0.6120145516650373</v>
       </c>
       <c r="E480">
-        <v>0.5111331468130343</v>
+        <v>0.5111331468130342</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -8528,7 +8528,7 @@
         <v>480</v>
       </c>
       <c r="B481">
-        <v>0.8580633277856055</v>
+        <v>0.8580633277856057</v>
       </c>
       <c r="C481">
         <v>0.7466535173094334</v>
@@ -8545,7 +8545,7 @@
         <v>481</v>
       </c>
       <c r="B482">
-        <v>0.8580633277856055</v>
+        <v>0.8580633277856057</v>
       </c>
       <c r="C482">
         <v>0.7466535173094334</v>
@@ -8599,7 +8599,7 @@
         <v>0.842500401959538</v>
       </c>
       <c r="C485">
-        <v>0.7288638761772981</v>
+        <v>0.7288638761772982</v>
       </c>
       <c r="D485">
         <v>0.6120145516650374</v>
@@ -8616,13 +8616,13 @@
         <v>0.8298611826909472</v>
       </c>
       <c r="C486">
-        <v>0.71848685733323</v>
+        <v>0.7184868573332301</v>
       </c>
       <c r="D486">
         <v>0.6079744058736298</v>
       </c>
       <c r="E486">
-        <v>0.5151136256016035</v>
+        <v>0.5151136256016033</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -8647,13 +8647,13 @@
         <v>487</v>
       </c>
       <c r="B488">
-        <v>0.7719515013385964</v>
+        <v>0.7719515013385965</v>
       </c>
       <c r="C488">
-        <v>0.6563050170415559</v>
+        <v>0.656305017041556</v>
       </c>
       <c r="D488">
-        <v>0.5467170805653965</v>
+        <v>0.5467170805653964</v>
       </c>
       <c r="E488">
         <v>0.4395193367095646</v>
@@ -8667,13 +8667,13 @@
         <v>0.7719515013385965</v>
       </c>
       <c r="C489">
-        <v>0.656305017041556</v>
+        <v>0.6563050170415561</v>
       </c>
       <c r="D489">
-        <v>0.5467170805653965</v>
+        <v>0.5467170805653964</v>
       </c>
       <c r="E489">
-        <v>0.4395193367095647</v>
+        <v>0.4395193367095646</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8681,13 +8681,13 @@
         <v>489</v>
       </c>
       <c r="B490">
-        <v>0.9047173797148154</v>
+        <v>0.9047173797148156</v>
       </c>
       <c r="C490">
-        <v>0.7940641908033091</v>
+        <v>0.7940641908033093</v>
       </c>
       <c r="D490">
-        <v>0.6973477655186987</v>
+        <v>0.6973477655186989</v>
       </c>
       <c r="E490">
         <v>0.609395055869833</v>
@@ -8698,13 +8698,13 @@
         <v>490</v>
       </c>
       <c r="B491">
-        <v>0.8933887922251891</v>
+        <v>0.8933887922251893</v>
       </c>
       <c r="C491">
-        <v>0.7707445081761158</v>
+        <v>0.7707445081761159</v>
       </c>
       <c r="D491">
-        <v>0.6764406247947327</v>
+        <v>0.6764406247947328</v>
       </c>
       <c r="E491">
         <v>0.5823461465878061</v>
@@ -8715,16 +8715,16 @@
         <v>491</v>
       </c>
       <c r="B492">
-        <v>0.9047173797148153</v>
+        <v>0.9047173797148156</v>
       </c>
       <c r="C492">
-        <v>0.794064190803309</v>
+        <v>0.7940641908033091</v>
       </c>
       <c r="D492">
         <v>0.6973477655186988</v>
       </c>
       <c r="E492">
-        <v>0.6093950558698331</v>
+        <v>0.609395055869833</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -8732,16 +8732,16 @@
         <v>492</v>
       </c>
       <c r="B493">
-        <v>0.9047173797148151</v>
+        <v>0.9047173797148154</v>
       </c>
       <c r="C493">
-        <v>0.794064190803309</v>
+        <v>0.7940641908033091</v>
       </c>
       <c r="D493">
         <v>0.6973477655186988</v>
       </c>
       <c r="E493">
-        <v>0.609395055869833</v>
+        <v>0.6093950558698329</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -8749,7 +8749,7 @@
         <v>493</v>
       </c>
       <c r="B494">
-        <v>0.9047173797148154</v>
+        <v>0.9047173797148156</v>
       </c>
       <c r="C494">
         <v>0.7940641908033091</v>
@@ -8775,7 +8775,7 @@
         <v>0.5548911858375353</v>
       </c>
       <c r="E495">
-        <v>0.4368779987297955</v>
+        <v>0.4368779987297954</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8786,7 +8786,7 @@
         <v>0.8427766704517561</v>
       </c>
       <c r="C496">
-        <v>0.7260645024839759</v>
+        <v>0.726064502483976</v>
       </c>
       <c r="D496">
         <v>0.6258173810214817</v>
@@ -8809,7 +8809,7 @@
         <v>0.5548911858375353</v>
       </c>
       <c r="E497">
-        <v>0.4368779987297955</v>
+        <v>0.4368779987297954</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8817,10 +8817,10 @@
         <v>497</v>
       </c>
       <c r="B498">
-        <v>0.817753620634885</v>
+        <v>0.8177536206348851</v>
       </c>
       <c r="C498">
-        <v>0.6953893525157693</v>
+        <v>0.6953893525157695</v>
       </c>
       <c r="D498">
         <v>0.5779713749709943</v>
@@ -8837,7 +8837,7 @@
         <v>0.817753620634885</v>
       </c>
       <c r="C499">
-        <v>0.6953893525157693</v>
+        <v>0.6953893525157696</v>
       </c>
       <c r="D499">
         <v>0.5779713749709943</v>
@@ -8854,7 +8854,7 @@
         <v>0.817753620634885</v>
       </c>
       <c r="C500">
-        <v>0.6953893525157693</v>
+        <v>0.6953893525157695</v>
       </c>
       <c r="D500">
         <v>0.5779713749709943</v>
@@ -8868,7 +8868,7 @@
         <v>500</v>
       </c>
       <c r="B501">
-        <v>0.8112507540966647</v>
+        <v>0.8112507540966648</v>
       </c>
       <c r="C501">
         <v>0.6896207167844964</v>

--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_OV_Fiets.xlsx
@@ -816,7 +816,7 @@
         <v>0.5811873114490647</v>
       </c>
       <c r="D27">
-        <v>0.5972269974804926</v>
+        <v>0.5972269974804925</v>
       </c>
       <c r="E27">
         <v>0.6137745967496684</v>
@@ -2057,7 +2057,7 @@
         <v>1.516583247643242</v>
       </c>
       <c r="D100">
-        <v>1.529333126980017</v>
+        <v>1.529333126980018</v>
       </c>
       <c r="E100">
         <v>1.184912134904824</v>
@@ -2346,7 +2346,7 @@
         <v>0.790160066527372</v>
       </c>
       <c r="D117">
-        <v>0.9490752879438371</v>
+        <v>0.949075287943837</v>
       </c>
       <c r="E117">
         <v>1.510675961315878</v>
@@ -3638,7 +3638,7 @@
         <v>1.119210944016345</v>
       </c>
       <c r="D193">
-        <v>1.232831673618838</v>
+        <v>1.232831673618839</v>
       </c>
       <c r="E193">
         <v>1.731116785042736</v>
@@ -5366,7 +5366,7 @@
         <v>294</v>
       </c>
       <c r="B295">
-        <v>0.8174381810071055</v>
+        <v>0.8174381810071056</v>
       </c>
       <c r="C295">
         <v>0.885316030106287</v>
@@ -5434,7 +5434,7 @@
         <v>298</v>
       </c>
       <c r="B299">
-        <v>0.8941391955291627</v>
+        <v>0.8941391955291628</v>
       </c>
       <c r="C299">
         <v>0.639246132037359</v>
@@ -5451,7 +5451,7 @@
         <v>299</v>
       </c>
       <c r="B300">
-        <v>0.7449879029610935</v>
+        <v>0.7449879029610936</v>
       </c>
       <c r="C300">
         <v>0.8924154705604304</v>
@@ -6086,7 +6086,7 @@
         <v>0.513664297251008</v>
       </c>
       <c r="D337">
-        <v>0.4848874116163825</v>
+        <v>0.4848874116163827</v>
       </c>
       <c r="E337">
         <v>0.4139489660201752</v>
